--- a/ EXERCISE DATABASE/workbook/EXERCISES.xlsx
+++ b/ EXERCISE DATABASE/workbook/EXERCISES.xlsx
@@ -8,24 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolashovsepyan/Library/CloudStorage/Dropbox/PERSONAL/COWORK/Fitness Journey - 2.0/ EXERCISE DATABASE/workbook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965495BD-E95A-FC44-8268-40DE9EF81B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6ACA02-CF9D-6941-B1FE-8717982901F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="40960" windowHeight="20740" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-40940" yWindow="-2400" windowWidth="29400" windowHeight="16740" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DO THIS NEXT" sheetId="1" r:id="rId1"/>
-    <sheet name="FUNDAMENTALS" sheetId="2" r:id="rId2"/>
-    <sheet name="CALIBRATION" sheetId="3" r:id="rId3"/>
-    <sheet name="MOVEMENTS" sheetId="4" r:id="rId4"/>
-    <sheet name="TRACKS" sheetId="5" r:id="rId5"/>
-    <sheet name="GYM LIBRARY" sheetId="6" r:id="rId6"/>
-    <sheet name="LISTS" sheetId="7" r:id="rId7"/>
-    <sheet name="GYM VERSIONS" sheetId="9" r:id="rId8"/>
+    <sheet name="4-DAY PROGRAM" sheetId="11" r:id="rId1"/>
+    <sheet name="DO THIS NEXT" sheetId="1" r:id="rId2"/>
+    <sheet name="FUNDAMENTALS" sheetId="2" r:id="rId3"/>
+    <sheet name="PPL PROGRAM" sheetId="12" r:id="rId4"/>
+    <sheet name="CALIBRATION" sheetId="3" r:id="rId5"/>
+    <sheet name="MOVEMENTS" sheetId="4" r:id="rId6"/>
+    <sheet name="TRACKS" sheetId="5" r:id="rId7"/>
+    <sheet name="GYM LIBRARY" sheetId="6" r:id="rId8"/>
+    <sheet name="LISTS" sheetId="7" r:id="rId9"/>
+    <sheet name="GYM VERSIONS" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CALIBRATION!$A$3:$M$98</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'GYM LIBRARY'!$A$3:$H$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">MOVEMENTS!$A$2:$AV$467</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">CALIBRATION!$A$3:$M$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'GYM LIBRARY'!$A$3:$H$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">MOVEMENTS!$A$2:$AV$467</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18351" uniqueCount="2200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18972" uniqueCount="2454">
   <si>
     <t>DO THIS NEXT</t>
   </si>
@@ -6649,13 +6651,778 @@
     <t>WINDSHIELD WIPERS ADDED at K26 — lie on your back, arms out wide for anchor, legs up, then lower them side to side under control. Rotation driven from the trunk against a long leg lever, and it needs nothing at all, which matters on this row: it is now the hardest ZERO-EQUIPMENT rung here. Bend the knees to make it easier, straighten the legs to make it harder.
 The row was full at 11 columns, so Half-Kneeling Cable Chop came out to make space — redundant with Cable Woodchop two rungs along, and you do not have cables.
 Anchor is Weighted Russian Twist (kettlebell or dumbbell). Entry rungs need no equipment: Thoracic Rotations → 90/90 Hip Switches → Russian Twist → Around-the-Body Pass → Half-Kneeling Rotation. CAVEAT unchanged: loaded and long-lever twisting both put the lumbar spine under rotation — keep the range moderate and the tempo slow.</t>
+  </si>
+  <si>
+    <t>4-DAY PROGRAM — 40 minutes, built only from the anchors on FUNDAMENTALS</t>
+  </si>
+  <si>
+    <t>Four days beats six at a 40-minute cap: every pattern still gets hit twice a week, each session stays hard, and there are four chances to miss instead of six. Session order follows Galpin — mobility, then the most neurally demanding work while fresh, then strength, then core. Every day is 50/50 lower/upper. Easier and Harder columns are live links to the ladder on FUNDAMENTALS, so a swap never leaves the system.</t>
+  </si>
+  <si>
+    <t>SESSION SHAPE — the same five blocks, every day</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Why it sits here</t>
+  </si>
+  <si>
+    <t>1 · Mobility &amp; prep</t>
+  </si>
+  <si>
+    <t>Open the hips, t-spine and shoulders first. Not a warm-up filler — it is the only mobility you get, so it is in the session, not optional.</t>
+  </si>
+  <si>
+    <t>2 · Explosive</t>
+  </si>
+  <si>
+    <t>Power is trained fresh or not at all. Low reps, full recovery, stop well short of fatigue — quality of each rep is the whole point.</t>
+  </si>
+  <si>
+    <t>3 · Primary pair A</t>
+  </si>
+  <si>
+    <t>Heaviest lower + heaviest upper, supersetted. The superset is what makes 40 minutes possible without cutting volume.</t>
+  </si>
+  <si>
+    <t>4 · Primary pair B</t>
+  </si>
+  <si>
+    <t>Second lower + second upper. Lighter, more reps, fills the pattern gaps the first pair left.</t>
+  </si>
+  <si>
+    <t>Working total</t>
+  </si>
+  <si>
+    <t>Leaves ~2 minutes for transitions inside the 40.</t>
+  </si>
+  <si>
+    <t>THE WEEK — every pattern twice, 50/50 lower/upper every single day</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Focus</t>
+  </si>
+  <si>
+    <t>Lower half</t>
+  </si>
+  <si>
+    <t>Upper half</t>
+  </si>
+  <si>
+    <t>Day 1 · Mon</t>
+  </si>
+  <si>
+    <t>Squat + horizontal</t>
+  </si>
+  <si>
+    <t>Goblet Squat, Bulgarian Split Squat</t>
+  </si>
+  <si>
+    <t>Push-Up, Wide Inverted Row</t>
+  </si>
+  <si>
+    <t>Day 2 · Tue</t>
+  </si>
+  <si>
+    <t>Hinge + vertical</t>
+  </si>
+  <si>
+    <t>Romanian Deadlift, Hip Thrust</t>
+  </si>
+  <si>
+    <t>Pull-Up, Pike Push-Up</t>
+  </si>
+  <si>
+    <t>Day 3 · Thu</t>
+  </si>
+  <si>
+    <t>Single-leg / frontal + horizontal</t>
+  </si>
+  <si>
+    <t>Cossack Squat, Reverse Nordic Curl</t>
+  </si>
+  <si>
+    <t>Dip, Wide Inverted Row</t>
+  </si>
+  <si>
+    <t>Day 4 · Sat</t>
+  </si>
+  <si>
+    <t>Posterior / isometric + vertical</t>
+  </si>
+  <si>
+    <t>Nordic Curl, Wall Sit</t>
+  </si>
+  <si>
+    <t>Wall Handstand, Dead Hang</t>
+  </si>
+  <si>
+    <t>Rest days</t>
+  </si>
+  <si>
+    <t>Wed, Fri, Sun</t>
+  </si>
+  <si>
+    <t>Walk or Zone 2 if you want it — nothing that needs recovery.</t>
+  </si>
+  <si>
+    <t>Sets</t>
+  </si>
+  <si>
+    <t>Reps / time</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Swap down (easier)</t>
+  </si>
+  <si>
+    <t>Swap up (harder)</t>
+  </si>
+  <si>
+    <t>The one thing that matters</t>
+  </si>
+  <si>
+    <t>DAY 1 — SQUAT + HORIZONTAL</t>
+  </si>
+  <si>
+    <t>1 · Mobility</t>
+  </si>
+  <si>
+    <t>5 / side</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Lunge, hand down, drive the top arm to the ceiling and follow it with your eyes. Hip and t-spine in one shape.</t>
+  </si>
+  <si>
+    <t>45 sec</t>
+  </si>
+  <si>
+    <t>Sit into the deepest squat you own and rock gently side to side. Buys the depth the goblet squat is about to ask for.</t>
+  </si>
+  <si>
+    <t>Hang, then pull the shoulders down away from the ears with straight arms. Wakes the lats before you row.</t>
+  </si>
+  <si>
+    <t>Jump Squat</t>
+  </si>
+  <si>
+    <t>90 sec</t>
+  </si>
+  <si>
+    <t>Maximum height, soft landing, reset fully between reps. The moment height drops, the set is over — this is not conditioning.</t>
+  </si>
+  <si>
+    <t>3 · Primary A</t>
+  </si>
+  <si>
+    <t>superset</t>
+  </si>
+  <si>
+    <t>Hip crease below the knee, chest tall. Load at the chest is what buys you the upright torso.</t>
+  </si>
+  <si>
+    <t>8–12</t>
+  </si>
+  <si>
+    <t>Chest to the floor, elbows 45°, push the floor away at the top. Leave 1–2 reps in the tank.</t>
+  </si>
+  <si>
+    <t>4 · Primary B</t>
+  </si>
+  <si>
+    <t>8 / leg</t>
+  </si>
+  <si>
+    <t>Front shin near vertical, back knee straight down. One leg loaded, spine unloaded.</t>
+  </si>
+  <si>
+    <t>75 sec</t>
+  </si>
+  <si>
+    <t>Wide grip, pull to the chest, squeeze the shoulder blades. Body stays one rigid line.</t>
+  </si>
+  <si>
+    <t>Day 1 total</t>
+  </si>
+  <si>
+    <t>DAY 2 — HINGE + VERTICAL</t>
+  </si>
+  <si>
+    <t>6 / side</t>
+  </si>
+  <si>
+    <t>Sit down, switch the legs side to side without using the hands. Internal and external hip rotation before you load the hinge.</t>
+  </si>
+  <si>
+    <t>8 / side</t>
+  </si>
+  <si>
+    <t>Rotate from the ribcage, not the low back. Pelvis stays still.</t>
+  </si>
+  <si>
+    <t>Hip flexor and hamstring in one shape — the two things about to limit your hinge.</t>
+  </si>
+  <si>
+    <t>60 sec</t>
+  </si>
+  <si>
+    <t>Hips snap the bell, arms are rope. Explosive hinge with no grinding — this is the power version of today's main lift.</t>
+  </si>
+  <si>
+    <t>Bar close, soft knees, hamstrings do the stretching. Stop where the spine wants to round.</t>
+  </si>
+  <si>
+    <t>max minus 1</t>
+  </si>
+  <si>
+    <t>Dead-hang start, chin over the bar, slow down. If you cannot get 3 clean reps, swap down.</t>
+  </si>
+  <si>
+    <t>Chin tucked, full lockout, hold the squeeze a beat. Glute in the shortened position — the half the RDL does not reach.</t>
+  </si>
+  <si>
+    <t>6–10</t>
+  </si>
+  <si>
+    <t>Hips high, head travels through the arms. Your only overhead press — do not rush it.</t>
+  </si>
+  <si>
+    <t>10 / side</t>
+  </si>
+  <si>
+    <t>Day 2 total</t>
+  </si>
+  <si>
+    <t>DAY 3 — SINGLE-LEG / FRONTAL + HORIZONTAL</t>
+  </si>
+  <si>
+    <t>Sit deep holding a light bell and pry the knees open with the elbows. Adductors, which today's main lift lives on.</t>
+  </si>
+  <si>
+    <t>Band above the knees, small steps, tension never drops. Wakes the glute in the frontal plane.</t>
+  </si>
+  <si>
+    <t>T-spine before the throw. Rotation should come from here, never the low back.</t>
+  </si>
+  <si>
+    <t>Throw it as hard as you can into a wall, hips leading. The only rotational power in the week — and the safest way to train twisting.</t>
+  </si>
+  <si>
+    <t>Working heel stays flat, other toes point up, chest tall. Depth over range — do not collapse to reach the floor.</t>
+  </si>
+  <si>
+    <t>Slight forward lean for chest, upright for triceps. Full depth, no shrugging into the ears.</t>
+  </si>
+  <si>
+    <t>Kneel tall, lean back from the knees only, hips locked open. Trains the lengthened quad no squat reaches.</t>
+  </si>
+  <si>
+    <t>Second horizontal-pull exposure of the week — go narrower and pull to the belly button so it is not a copy of Day 1.</t>
+  </si>
+  <si>
+    <t>Day 3 total</t>
+  </si>
+  <si>
+    <t>DAY 4 — POSTERIOR / ISOMETRIC + VERTICAL</t>
+  </si>
+  <si>
+    <t>Hamstring and hip flexor open before the hardest hamstring day of the week.</t>
+  </si>
+  <si>
+    <t>Hip rotation both directions. Cheap insurance on a day with a lot of knee flexion.</t>
+  </si>
+  <si>
+    <t>Shoulders long, then pull them down. Prepares the overhead and hanging work coming up.</t>
+  </si>
+  <si>
+    <t>Power Clean to Overhead Press</t>
+  </si>
+  <si>
+    <t>Light and fast. Triple extension, catch tall, press. If the bar slows down, stop the set — technique is the training effect.</t>
+  </si>
+  <si>
+    <t>— no harder rung exists yet</t>
+  </si>
+  <si>
+    <t>Control the eccentric, catch with the hands. Progress range first, then load. Hardest movement in the program — swap down without ego.</t>
+  </si>
+  <si>
+    <t>30 sec</t>
+  </si>
+  <si>
+    <t>Straight line ears-hips-heels, push the floor away, gaze down. Overhead strength without a press.</t>
+  </si>
+  <si>
+    <t>45–60 sec</t>
+  </si>
+  <si>
+    <t>— nothing easier exists</t>
+  </si>
+  <si>
+    <t>Thighs parallel, knees over ankles, weight in the heels, breathe normally. Scored in seconds — that is the point.</t>
+  </si>
+  <si>
+    <t>Full grip, shoulders long, ribs down, no shrugging. Grip is the thing that caps every pull in this program.</t>
+  </si>
+  <si>
+    <t>Day 4 total</t>
+  </si>
+  <si>
+    <t>Half</t>
+  </si>
+  <si>
+    <t>Upper</t>
+  </si>
+  <si>
+    <t>BALANCE CHECK — counted from column K, not claimed</t>
+  </si>
+  <si>
+    <t>Slots / week</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Weekly training time (min)</t>
+  </si>
+  <si>
+    <t>Working minutes only. Add ~2 min per day for transitions → 40-minute doors.</t>
+  </si>
+  <si>
+    <t>Patterns hit twice a week</t>
+  </si>
+  <si>
+    <t>Squat (D1 Goblet, D3 Cossack) · Hinge (D2 RDL+Swing, D4 Nordic) · Single-leg (D1 Bulgarian, D3 Cossack) · H-push (D1 Push-Up, D3 Dip) · V-push (D2 Pike, D4 Handstand) · H-pull (D1, D3 Inverted Row) · V-pull (D2 Pull-Up, D4 Dead Hang/HLR) · Core (all four)</t>
+  </si>
+  <si>
+    <t>Explosive exposures</t>
+  </si>
+  <si>
+    <t>4 — one per day, always fresh: vertical jump, hinge power, rotational power, full triple extension.</t>
+  </si>
+  <si>
+    <t>Mobility exposures</t>
+  </si>
+  <si>
+    <t>12 — three per day, always the joints that limit that day's lifts.</t>
+  </si>
+  <si>
+    <t>5 · Circuit finisher</t>
+  </si>
+  <si>
+    <t>Always ends the same way: a timed circuit, three movements, at least two of them core. Core is no longer one afterthought set — it is the finisher, and the clock does the pushing so you cannot quietly cut it short.</t>
+  </si>
+  <si>
+    <t>CIRCUIT FORMATS — what the finisher labels mean</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>How to run it</t>
+  </si>
+  <si>
+    <t>AMRAP 8</t>
+  </si>
+  <si>
+    <t>As Many Rounds As Possible in 8 minutes. Move through the three movements in order, rest only when you have to, write the rounds down. Beat that number next week.</t>
+  </si>
+  <si>
+    <t>EMOM 8</t>
+  </si>
+  <si>
+    <t>4 RFT (cap 8)</t>
+  </si>
+  <si>
+    <t>4 Rounds For Time, 8-minute cap. Fixed work, race the clock. If the cap comes first, that is your score — no shaving reps to beat it.</t>
+  </si>
+  <si>
+    <t>Tabata 8</t>
+  </si>
+  <si>
+    <t>20 seconds hard, 10 seconds off, 16 intervals, rotating through the three movements. Your score is the WEAKEST interval — so pace it from round one.</t>
+  </si>
+  <si>
+    <t>Rule for all four</t>
+  </si>
+  <si>
+    <t>Form is the cap, not the clock. The moment a core position breaks — low back arching, hip sagging, swinging on the bar — that interval is over. Take the rest.</t>
+  </si>
+  <si>
+    <t>5 · Finisher · AMRAP 8</t>
+  </si>
+  <si>
+    <t>no rest</t>
+  </si>
+  <si>
+    <t>Low back pressed flat, ribs closed. Round 1 is easy and round 4 is not — bend the knees to hold the shape rather than arching.</t>
+  </si>
+  <si>
+    <t>20 sec / side</t>
+  </si>
+  <si>
+    <t>Hip stacked and lifted. Second core angle of the circuit — front, then side.</t>
+  </si>
+  <si>
+    <t>then repeat</t>
+  </si>
+  <si>
+    <t>The engine piece that turns two core holds into a finisher. Chest to floor, full stand at the top, no half reps when it starts to hurt.</t>
+  </si>
+  <si>
+    <t>Cond</t>
+  </si>
+  <si>
+    <t>Every Minute On the Minute. One movement per minute, rotating through the list; whatever is left of the minute is your rest. Faster you work, more rest you earn.</t>
+  </si>
+  <si>
+    <t>5 · Finisher · EMOM 8</t>
+  </si>
+  <si>
+    <t>min 1</t>
+  </si>
+  <si>
+    <t>rest of the min</t>
+  </si>
+  <si>
+    <t>Anti-rotation first, while you are freshest. Nothing moves but the arms — the clock is not an excuse to twist.</t>
+  </si>
+  <si>
+    <t>min 2</t>
+  </si>
+  <si>
+    <t>Turn the ribcage, do not swing the arms. This is the only loaded rotation in the week — keep the range moderate and the tempo honest.</t>
+  </si>
+  <si>
+    <t>min 3</t>
+  </si>
+  <si>
+    <t>40 sec</t>
+  </si>
+  <si>
+    <t>then back to min 1</t>
+  </si>
+  <si>
+    <t>— lighter load</t>
+  </si>
+  <si>
+    <t>Heavy, ribs down, do not lean. A carry is core work standing up — and it is the grip insurance for Day 4.</t>
+  </si>
+  <si>
+    <t>5 · Finisher · 4 RFT (cap 8)</t>
+  </si>
+  <si>
+    <t>Rock from the shoulders, not the hips — the hollow shape never changes. If it breaks, drop back to a static hold.</t>
+  </si>
+  <si>
+    <t>Dip the hip to the floor and drive it back up. Oblique work with movement, not just a hold — matches the frontal-plane legs above.</t>
+  </si>
+  <si>
+    <t>— lighter bell</t>
+  </si>
+  <si>
+    <t>— heavier bell</t>
+  </si>
+  <si>
+    <t>Hips snap, arms are rope. Also the only hinge on Day 3 — it patches the pattern this day is missing.</t>
+  </si>
+  <si>
+    <t>5 · Finisher · Tabata 8</t>
+  </si>
+  <si>
+    <t>20 sec on / 10 off</t>
+  </si>
+  <si>
+    <t>10 sec</t>
+  </si>
+  <si>
+    <t>No swing, tilt the pelvis at the top. Straight off the hang you were just in — grip will fail before the abs do, and that is the point.</t>
+  </si>
+  <si>
+    <t>Lower as one rigid plank, hips never bend. End the interval the moment the hips break — a bad Dragon Flag is just a back extension.</t>
+  </si>
+  <si>
+    <t>then back to the top</t>
+  </si>
+  <si>
+    <t>— knees down</t>
+  </si>
+  <si>
+    <t>The recovery station of the circuit — hold the shape and breathe. Glutes on, ribs down, no sagging.</t>
+  </si>
+  <si>
+    <t>Core slots (in the finishers)</t>
+  </si>
+  <si>
+    <t>Was 4 before the reshape. Every day now ends on 2–3 core movements instead of one set.</t>
+  </si>
+  <si>
+    <t>Conditioning slots</t>
+  </si>
+  <si>
+    <t>Burpee (D1) and Kettlebell Swing (D3) — the engine pieces that turn core holds into a finisher.</t>
+  </si>
+  <si>
+    <t>Circuit finishers</t>
+  </si>
+  <si>
+    <t>4 — one per day, never skipped: AMRAP 8, EMOM 8, 4 Rounds For Time, Tabata 8. Different clock every day so the stimulus does not go stale.</t>
+  </si>
+  <si>
+    <t>Circuit finisher (core-led)</t>
+  </si>
+  <si>
+    <t>AMRAP 8 — Hollow Hold + Side Plank + Burpee</t>
+  </si>
+  <si>
+    <t>EMOM 8 — Pallof Press + Russian Twist + Farmer's Carry</t>
+  </si>
+  <si>
+    <t>4 RFT — Hollow Rock + Side Plank Hip Dip + KB Swing</t>
+  </si>
+  <si>
+    <t>Tabata 8 — Hanging Leg Raise + Dragon Flag (Tuck) + Plank</t>
+  </si>
+  <si>
+    <t>PPL PROGRAM — Push / Pull / Lower, 4 days, 40 minutes</t>
+  </si>
+  <si>
+    <t>Same engine as the 4-DAY PROGRAM, different split. Here push and pull are never in the same session — each gets the upper half of two days, so you get concentrated push volume and concentrated pull volume instead of one of each every day. Lower work appears every single day, which is what keeps it 50/50 without needing a fifth or sixth session. Every day ends on a circuit finisher.</t>
+  </si>
+  <si>
+    <t>Joint prep aimed at the day's own limiters — shoulders and t-spine on push/pull days, hips on every day.</t>
+  </si>
+  <si>
+    <t>Power first, while the nervous system is fresh. Low reps, full recovery, stop before fatigue shows up in the reps.</t>
+  </si>
+  <si>
+    <t>Hardest upper of the day paired with the hardest lower. Supersetted — that pairing is the only reason this fits in 40 minutes.</t>
+  </si>
+  <si>
+    <t>Second upper (same push-or-pull family) + second lower. Lighter, higher reps, fills what the first pair missed.</t>
+  </si>
+  <si>
+    <t>Timed circuit, three movements, at least two of them core. The clock does the pushing, so core never gets quietly dropped.</t>
+  </si>
+  <si>
+    <t>THE WEEK — push twice, pull twice, lower every day, 50/50 by slots</t>
+  </si>
+  <si>
+    <t>PUSH + squat</t>
+  </si>
+  <si>
+    <t>Dip, Pike Push-Up</t>
+  </si>
+  <si>
+    <t>PULL + hinge</t>
+  </si>
+  <si>
+    <t>Pull-Up, Wide Inverted Row</t>
+  </si>
+  <si>
+    <t>EMOM 8 — Hanging Leg Raise + Pallof Press + Farmer's Carry</t>
+  </si>
+  <si>
+    <t>PUSH + single-leg</t>
+  </si>
+  <si>
+    <t>Push-Up, Wall Handstand</t>
+  </si>
+  <si>
+    <t>4 RFT — Hollow Rock + Russian Twist + KB Swing</t>
+  </si>
+  <si>
+    <t>PULL + posterior/iso</t>
+  </si>
+  <si>
+    <t>Band-Assisted Front Lever, Dead Hang</t>
+  </si>
+  <si>
+    <t>Tabata 8 — Dragon Flag (Tuck) + Side Plank Hip Dip + Plank</t>
+  </si>
+  <si>
+    <t>Walk or Zone 2 only — nothing that needs recovery.</t>
+  </si>
+  <si>
+    <t>DAY 1 — PUSH + SQUAT</t>
+  </si>
+  <si>
+    <t>Hang and pull the shoulders down with straight arms. Scapular control before you load the shoulder overhead.</t>
+  </si>
+  <si>
+    <t>Rotate from the ribcage. A stiff t-spine is what turns a pike press into a low-back arch.</t>
+  </si>
+  <si>
+    <t>Locked out on the bars, shoulders down, ribs in. Cheapest way to make the first dip set safe.</t>
+  </si>
+  <si>
+    <t>Light and fast. Triple extension, catch tall, press. If the bar slows, the set is done — speed is the training effect.</t>
+  </si>
+  <si>
+    <t>Slight lean for chest, upright for triceps. Full depth, no shrugging. Hardest push you own — it goes first.</t>
+  </si>
+  <si>
+    <t>Hip crease below the knee, chest tall. The load at the chest is what buys the upright torso.</t>
+  </si>
+  <si>
+    <t>Hips high, head travels through the arms. Vertical push after horizontal — same day, different angle.</t>
+  </si>
+  <si>
+    <t>Low back flat, ribs closed. Bend the knees to keep the shape rather than arching to hold the time.</t>
+  </si>
+  <si>
+    <t>Hip stacked and lifted, not sagging. Front shape, then side shape.</t>
+  </si>
+  <si>
+    <t>Chest to floor, full stand at the top. The engine piece — no half reps once it starts to hurt.</t>
+  </si>
+  <si>
+    <t>DAY 2 — PULL + HINGE</t>
+  </si>
+  <si>
+    <t>Shoulders long, then pull them down. This is the pull day's first rep, not a warm-up formality.</t>
+  </si>
+  <si>
+    <t>Switch the legs side to side without the hands. Hip rotation before the loaded hinge.</t>
+  </si>
+  <si>
+    <t>Hang with the shoulders engaged, ribs down. Decompresses the spine and switches the lats on.</t>
+  </si>
+  <si>
+    <t>Hips snap the bell, arms are rope. Explosive hinge with no grinding — the power version of today's main lift.</t>
+  </si>
+  <si>
+    <t>Dead-hang start, chin over the bar, slow down. Under 3 clean reps means swap down, not swing harder.</t>
+  </si>
+  <si>
+    <t>10–12</t>
+  </si>
+  <si>
+    <t>Wide grip, pull to the chest, body one rigid line. Horizontal pull after vertical — both angles, one day.</t>
+  </si>
+  <si>
+    <t>Chin tucked, full lockout, hold the squeeze a beat. The shortened-glute half the RDL cannot reach.</t>
+  </si>
+  <si>
+    <t>No swing, tilt the pelvis at the top, lower slowly. Straight off a pull day — grip will be the limit, not the abs.</t>
+  </si>
+  <si>
+    <t>The band wants to twist you; refuse. Nothing moves but the arms — the clock is not an excuse.</t>
+  </si>
+  <si>
+    <t>Heavy, ribs down, do not lean. Core standing up — and more grip work on the day that needs it.</t>
+  </si>
+  <si>
+    <t>DAY 3 — PUSH + SINGLE-LEG</t>
+  </si>
+  <si>
+    <t>Sit deep with a light bell and pry the knees open with the elbows. Adductors, which today's squat lives on.</t>
+  </si>
+  <si>
+    <t>Band above the knees, small steps, tension never drops. Wakes the glute sideways.</t>
+  </si>
+  <si>
+    <t>T-spine before the throw and before anything overhead. Rotation from here, never the low back.</t>
+  </si>
+  <si>
+    <t>Throw it into a wall as hard as you can, hips leading. The only rotational power in the week and the safest way to train twisting.</t>
+  </si>
+  <si>
+    <t>10–15</t>
+  </si>
+  <si>
+    <t>Chest to floor, elbows 45°, push the floor away at the top. Volume day for push — Day 1 was the heavy one.</t>
+  </si>
+  <si>
+    <t>Working heel flat, other toes up, chest tall. Control over range — do not collapse to reach the floor.</t>
+  </si>
+  <si>
+    <t>Kneel tall, lean back from the knees only, hips locked open. The lengthened quad no squat reaches.</t>
+  </si>
+  <si>
+    <t>Rock from the shoulders, hollow shape never changes. If it breaks, drop to a static hold and finish the round.</t>
+  </si>
+  <si>
+    <t>Turn the ribcage, do not swing the arms. Moderate range, honest tempo — loaded twisting is the one thing here to be careful with.</t>
+  </si>
+  <si>
+    <t>DAY 4 — PULL + POSTERIOR / ISOMETRIC</t>
+  </si>
+  <si>
+    <t>Hip rotation both directions. Cheap insurance on a day full of knee flexion.</t>
+  </si>
+  <si>
+    <t>20–30 sec</t>
+  </si>
+  <si>
+    <t>Hang with the shoulders behind you, go slowly and never force it. Opens the exact position the lever work asks for.</t>
+  </si>
+  <si>
+    <t>Maximum height, soft landing, full reset. Height drops, set over — this is not conditioning.</t>
+  </si>
+  <si>
+    <t>15–20 sec</t>
+  </si>
+  <si>
+    <t>Straight arms, body one line, band under the hips. Tier 3 — if you cannot hold a clean tuck, start at the swap-down and do not force this one.</t>
+  </si>
+  <si>
+    <t>Control the eccentric, catch with the hands. Range first, then load. Hardest movement in either program — swap down without ego.</t>
+  </si>
+  <si>
+    <t>Full grip, shoulders long, ribs down, no shrugging. Grip is what caps every pull in this program.</t>
+  </si>
+  <si>
+    <t>Dip the hip to the floor and drive it back up. Oblique work with movement, not just a hold.</t>
+  </si>
+  <si>
+    <t>Two to three every day — core is the finisher, not a leftover set.</t>
+  </si>
+  <si>
+    <t>Burpee (D1) and Kettlebell Swing (D3).</t>
+  </si>
+  <si>
+    <t>Push frequency</t>
+  </si>
+  <si>
+    <t>2 × week — Day 1 heavy (Dip, Pike Push-Up), Day 3 volume (Push-Up, Wall Handstand). Both horizontal and vertical each time.</t>
+  </si>
+  <si>
+    <t>Pull frequency</t>
+  </si>
+  <si>
+    <t>2 × week — Day 2 (Pull-Up, Inverted Row), Day 4 (Front Lever, Dead Hang). Vertical, horizontal, straight-arm and grip all covered.</t>
+  </si>
+  <si>
+    <t>Lower frequency</t>
+  </si>
+  <si>
+    <t>4 × week, one pattern per day: squat (D1), hinge (D2), single-leg / frontal (D3), posterior + isometric (D4).</t>
+  </si>
+  <si>
+    <t>4 — AMRAP 8, EMOM 8, 4 Rounds For Time, Tabata 8. Different clock every day.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6849,8 +7616,54 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7015,6 +7828,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -7054,7 +7897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -7197,14 +8040,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7220,10 +8058,6 @@
     <xf numFmtId="0" fontId="22" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7232,34 +8066,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7268,25 +8101,22 @@
     <xf numFmtId="0" fontId="3" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7296,13 +8126,99 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7636,6 +8552,3264 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161F9CE4-2512-BE4C-A57E-8ABBE8CB87B4}">
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="95" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
+    <col min="10" max="10" width="72.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="101" t="s">
+        <v>2200</v>
+      </c>
+      <c r="J1" s="109"/>
+    </row>
+    <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="104" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="104"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J3" s="109"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="102" t="s">
+        <v>2202</v>
+      </c>
+      <c r="J4" s="109"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="105" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C5" s="105" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>2205</v>
+      </c>
+      <c r="J5" s="109"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2207</v>
+      </c>
+      <c r="J6" s="109"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2209</v>
+      </c>
+      <c r="J7" s="109"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>2210</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2211</v>
+      </c>
+      <c r="J8" s="109"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>2212</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2213</v>
+      </c>
+      <c r="J9" s="109"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2323</v>
+      </c>
+      <c r="J10" s="109"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="102" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C11" s="102">
+        <f>SUM(C6:C10)</f>
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2215</v>
+      </c>
+      <c r="J11" s="109"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J12" s="109"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="102" t="s">
+        <v>2216</v>
+      </c>
+      <c r="J13" s="109"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="105" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E14" s="105" t="s">
+        <v>2220</v>
+      </c>
+      <c r="F14" s="105" t="s">
+        <v>2376</v>
+      </c>
+      <c r="J14" s="109"/>
+    </row>
+    <row r="15" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2222</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F15" s="109" t="s">
+        <v>2377</v>
+      </c>
+      <c r="J15" s="109"/>
+    </row>
+    <row r="16" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F16" s="109" t="s">
+        <v>2378</v>
+      </c>
+      <c r="J16" s="109"/>
+    </row>
+    <row r="17" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2230</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2232</v>
+      </c>
+      <c r="F17" s="109" t="s">
+        <v>2379</v>
+      </c>
+      <c r="J17" s="109"/>
+    </row>
+    <row r="18" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2234</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2236</v>
+      </c>
+      <c r="F18" s="109" t="s">
+        <v>2380</v>
+      </c>
+      <c r="J18" s="109"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2239</v>
+      </c>
+      <c r="J19" s="109"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J20" s="109"/>
+    </row>
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="110" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B21" s="110" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C21" s="110" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" s="110" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E21" s="110" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F21" s="110" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G21" s="110" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H21" s="110" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I21" s="110" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J21" s="111" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K21" s="110" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="112" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="113"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="112"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="112"/>
+    </row>
+    <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A23" s="115">
+        <v>1</v>
+      </c>
+      <c r="B23" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C23" s="116" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="117">
+        <v>1</v>
+      </c>
+      <c r="E23" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G23" s="117">
+        <v>5</v>
+      </c>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="118" t="s">
+        <v>2250</v>
+      </c>
+      <c r="K23" s="115"/>
+    </row>
+    <row r="24" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="115">
+        <v>1</v>
+      </c>
+      <c r="B24" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C24" s="116" t="str">
+        <f>FUNDAMENTALS!E11</f>
+        <v>Deep Squat Rocks</v>
+      </c>
+      <c r="D24" s="117">
+        <v>1</v>
+      </c>
+      <c r="E24" s="117" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F24" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G24" s="117"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="118" t="s">
+        <v>2252</v>
+      </c>
+      <c r="K24" s="115"/>
+    </row>
+    <row r="25" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="115">
+        <v>1</v>
+      </c>
+      <c r="B25" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C25" s="116" t="str">
+        <f>FUNDAMENTALS!E21</f>
+        <v>Scapular Pull-ups</v>
+      </c>
+      <c r="D25" s="117">
+        <v>1</v>
+      </c>
+      <c r="E25" s="117">
+        <v>8</v>
+      </c>
+      <c r="F25" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G25" s="117"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="118" t="s">
+        <v>2253</v>
+      </c>
+      <c r="K25" s="115"/>
+    </row>
+    <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="115">
+        <v>1</v>
+      </c>
+      <c r="B26" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C26" s="116" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D26" s="117">
+        <v>3</v>
+      </c>
+      <c r="E26" s="117">
+        <v>5</v>
+      </c>
+      <c r="F26" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G26" s="117">
+        <v>5</v>
+      </c>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="118" t="s">
+        <v>2256</v>
+      </c>
+      <c r="K26" s="115"/>
+    </row>
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="115">
+        <v>1</v>
+      </c>
+      <c r="B27" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C27" s="116" t="str">
+        <f>FUNDAMENTALS!I5</f>
+        <v>Goblet Squat</v>
+      </c>
+      <c r="D27" s="117">
+        <v>3</v>
+      </c>
+      <c r="E27" s="117">
+        <v>8</v>
+      </c>
+      <c r="F27" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G27" s="117">
+        <v>11</v>
+      </c>
+      <c r="H27" s="116" t="str">
+        <f>FUNDAMENTALS!H5</f>
+        <v>Slant-Board Squat</v>
+      </c>
+      <c r="I27" s="116" t="str">
+        <f>FUNDAMENTALS!J5</f>
+        <v>Back Squat</v>
+      </c>
+      <c r="J27" s="118" t="s">
+        <v>2259</v>
+      </c>
+      <c r="K27" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="115">
+        <v>1</v>
+      </c>
+      <c r="B28" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C28" s="116" t="str">
+        <f>FUNDAMENTALS!I14</f>
+        <v>Push-ups</v>
+      </c>
+      <c r="D28" s="117">
+        <v>3</v>
+      </c>
+      <c r="E28" s="117" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F28" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G28" s="117"/>
+      <c r="H28" s="116" t="str">
+        <f>FUNDAMENTALS!H14</f>
+        <v>Knee Push-Up</v>
+      </c>
+      <c r="I28" s="116" t="str">
+        <f>FUNDAMENTALS!J14</f>
+        <v>Decline Push-Up</v>
+      </c>
+      <c r="J28" s="118" t="s">
+        <v>2261</v>
+      </c>
+      <c r="K28" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="115">
+        <v>1</v>
+      </c>
+      <c r="B29" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C29" s="116" t="str">
+        <f>FUNDAMENTALS!I8</f>
+        <v>Bulgarian Split Squat</v>
+      </c>
+      <c r="D29" s="117">
+        <v>3</v>
+      </c>
+      <c r="E29" s="117" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F29" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G29" s="117">
+        <v>9</v>
+      </c>
+      <c r="H29" s="116" t="str">
+        <f>FUNDAMENTALS!H8</f>
+        <v>Racked Reverse Lunge</v>
+      </c>
+      <c r="I29" s="116" t="str">
+        <f>FUNDAMENTALS!J8</f>
+        <v>Barbell Bulgarian Split Squat</v>
+      </c>
+      <c r="J29" s="118" t="s">
+        <v>2264</v>
+      </c>
+      <c r="K29" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="115">
+        <v>1</v>
+      </c>
+      <c r="B30" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C30" s="116" t="str">
+        <f>FUNDAMENTALS!I20</f>
+        <v>Wide Inverted Row</v>
+      </c>
+      <c r="D30" s="117">
+        <v>3</v>
+      </c>
+      <c r="E30" s="117">
+        <v>10</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G30" s="117"/>
+      <c r="H30" s="116" t="str">
+        <f>FUNDAMENTALS!H20</f>
+        <v>Australian Pull-Up</v>
+      </c>
+      <c r="I30" s="116" t="str">
+        <f>FUNDAMENTALS!J20</f>
+        <v>Feet-Elevated Ring Row</v>
+      </c>
+      <c r="J30" s="118" t="s">
+        <v>2266</v>
+      </c>
+      <c r="K30" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="126">
+        <v>1</v>
+      </c>
+      <c r="B31" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C31" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="D31" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E31" s="128" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F31" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G31" s="128">
+        <v>8</v>
+      </c>
+      <c r="H31" s="127" t="str">
+        <f>FUNDAMENTALS!H24</f>
+        <v>Forearm Plank</v>
+      </c>
+      <c r="I31" s="127" t="str">
+        <f>FUNDAMENTALS!J24</f>
+        <v>Hollow Rock</v>
+      </c>
+      <c r="J31" s="129" t="s">
+        <v>2338</v>
+      </c>
+      <c r="K31" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="126">
+        <v>1</v>
+      </c>
+      <c r="B32" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C32" s="127" t="str">
+        <f>FUNDAMENTALS!I25</f>
+        <v>Side Plank</v>
+      </c>
+      <c r="D32" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E32" s="128" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F32" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G32" s="128"/>
+      <c r="H32" s="127" t="str">
+        <f>FUNDAMENTALS!H25</f>
+        <v>Side Plank (hand on bar)</v>
+      </c>
+      <c r="I32" s="127" t="str">
+        <f>FUNDAMENTALS!J25</f>
+        <v>Side Plank Hip Dip</v>
+      </c>
+      <c r="J32" s="129" t="s">
+        <v>2340</v>
+      </c>
+      <c r="K32" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A33" s="126">
+        <v>1</v>
+      </c>
+      <c r="B33" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C33" s="130" t="s">
+        <v>332</v>
+      </c>
+      <c r="D33" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E33" s="128">
+        <v>8</v>
+      </c>
+      <c r="F33" s="128" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G33" s="128"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="129" t="s">
+        <v>2342</v>
+      </c>
+      <c r="K33" s="126" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="119"/>
+      <c r="B34" s="119" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120">
+        <f>SUM(G23:G31)</f>
+        <v>38</v>
+      </c>
+      <c r="H34" s="119"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="121"/>
+      <c r="K34" s="119"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A35" s="115"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="115"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="115"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="112" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B36" s="112"/>
+      <c r="C36" s="112"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
+      <c r="H36" s="112"/>
+      <c r="I36" s="112"/>
+      <c r="J36" s="114"/>
+      <c r="K36" s="112"/>
+    </row>
+    <row r="37" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A37" s="115">
+        <v>2</v>
+      </c>
+      <c r="B37" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C37" s="116" t="str">
+        <f>FUNDAMENTALS!E26</f>
+        <v>90/90 Hip Switches</v>
+      </c>
+      <c r="D37" s="117">
+        <v>1</v>
+      </c>
+      <c r="E37" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F37" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G37" s="117">
+        <v>5</v>
+      </c>
+      <c r="H37" s="116"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="118" t="s">
+        <v>2270</v>
+      </c>
+      <c r="K37" s="115"/>
+    </row>
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="115">
+        <v>2</v>
+      </c>
+      <c r="B38" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C38" s="116" t="str">
+        <f>FUNDAMENTALS!D26</f>
+        <v>Thoracic Rotations</v>
+      </c>
+      <c r="D38" s="117">
+        <v>1</v>
+      </c>
+      <c r="E38" s="117" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F38" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G38" s="117"/>
+      <c r="H38" s="116"/>
+      <c r="I38" s="116"/>
+      <c r="J38" s="118" t="s">
+        <v>2272</v>
+      </c>
+      <c r="K38" s="115"/>
+    </row>
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="115">
+        <v>2</v>
+      </c>
+      <c r="B39" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C39" s="116" t="s">
+        <v>360</v>
+      </c>
+      <c r="D39" s="117">
+        <v>1</v>
+      </c>
+      <c r="E39" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F39" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G39" s="117"/>
+      <c r="H39" s="116"/>
+      <c r="I39" s="116"/>
+      <c r="J39" s="118" t="s">
+        <v>2273</v>
+      </c>
+      <c r="K39" s="115"/>
+    </row>
+    <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A40" s="115">
+        <v>2</v>
+      </c>
+      <c r="B40" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C40" s="116" t="str">
+        <f>FUNDAMENTALS!J6</f>
+        <v>Kettlebell Swing</v>
+      </c>
+      <c r="D40" s="117">
+        <v>5</v>
+      </c>
+      <c r="E40" s="117">
+        <v>8</v>
+      </c>
+      <c r="F40" s="117" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G40" s="117">
+        <v>5</v>
+      </c>
+      <c r="H40" s="116"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="118" t="s">
+        <v>2275</v>
+      </c>
+      <c r="K40" s="115"/>
+    </row>
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="115">
+        <v>2</v>
+      </c>
+      <c r="B41" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C41" s="116" t="str">
+        <f>FUNDAMENTALS!I6</f>
+        <v>Romanian Deadlift</v>
+      </c>
+      <c r="D41" s="117">
+        <v>3</v>
+      </c>
+      <c r="E41" s="117">
+        <v>8</v>
+      </c>
+      <c r="F41" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G41" s="117">
+        <v>11</v>
+      </c>
+      <c r="H41" s="116" t="str">
+        <f>FUNDAMENTALS!H6</f>
+        <v>Dumbbell Romanian Deadlift</v>
+      </c>
+      <c r="I41" s="116" t="str">
+        <f>FUNDAMENTALS!K6</f>
+        <v>Single-Leg RDL</v>
+      </c>
+      <c r="J41" s="118" t="s">
+        <v>2276</v>
+      </c>
+      <c r="K41" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="115">
+        <v>2</v>
+      </c>
+      <c r="B42" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C42" s="116" t="str">
+        <f>FUNDAMENTALS!I21</f>
+        <v>Pull-Up</v>
+      </c>
+      <c r="D42" s="117">
+        <v>3</v>
+      </c>
+      <c r="E42" s="117" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F42" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G42" s="117"/>
+      <c r="H42" s="116" t="str">
+        <f>FUNDAMENTALS!H21</f>
+        <v>Negative Pull-Up</v>
+      </c>
+      <c r="I42" s="116" t="str">
+        <f>FUNDAMENTALS!J21</f>
+        <v>Wide-Grip Pull-Up</v>
+      </c>
+      <c r="J42" s="118" t="s">
+        <v>2278</v>
+      </c>
+      <c r="K42" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="115">
+        <v>2</v>
+      </c>
+      <c r="B43" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C43" s="116" t="str">
+        <f>FUNDAMENTALS!I7</f>
+        <v>Hip Thrust</v>
+      </c>
+      <c r="D43" s="117">
+        <v>3</v>
+      </c>
+      <c r="E43" s="117">
+        <v>10</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G43" s="117">
+        <v>9</v>
+      </c>
+      <c r="H43" s="116" t="str">
+        <f>FUNDAMENTALS!H7</f>
+        <v>Banded Glute Bridge</v>
+      </c>
+      <c r="I43" s="116" t="str">
+        <f>FUNDAMENTALS!J7</f>
+        <v>Barbell Hip Thrust</v>
+      </c>
+      <c r="J43" s="118" t="s">
+        <v>2279</v>
+      </c>
+      <c r="K43" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="115">
+        <v>2</v>
+      </c>
+      <c r="B44" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C44" s="116" t="str">
+        <f>FUNDAMENTALS!I15</f>
+        <v>Pike Push-Up</v>
+      </c>
+      <c r="D44" s="117">
+        <v>3</v>
+      </c>
+      <c r="E44" s="117" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F44" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G44" s="117"/>
+      <c r="H44" s="116" t="str">
+        <f>FUNDAMENTALS!H15</f>
+        <v>Incline Push-Up</v>
+      </c>
+      <c r="I44" s="116" t="str">
+        <f>FUNDAMENTALS!J15</f>
+        <v>Elevated Pike Push-Up</v>
+      </c>
+      <c r="J44" s="118" t="s">
+        <v>2281</v>
+      </c>
+      <c r="K44" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A45" s="126">
+        <v>2</v>
+      </c>
+      <c r="B45" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C45" s="127" t="str">
+        <f>FUNDAMENTALS!I27</f>
+        <v>Pallof Press</v>
+      </c>
+      <c r="D45" s="128" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E45" s="128" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F45" s="128" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G45" s="128">
+        <v>8</v>
+      </c>
+      <c r="H45" s="127" t="str">
+        <f>FUNDAMENTALS!H27</f>
+        <v>Bird Dog</v>
+      </c>
+      <c r="I45" s="127" t="str">
+        <f>FUNDAMENTALS!J27</f>
+        <v>Half-Kneeling Cable Chop</v>
+      </c>
+      <c r="J45" s="129" t="s">
+        <v>2348</v>
+      </c>
+      <c r="K45" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="126">
+        <v>2</v>
+      </c>
+      <c r="B46" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C46" s="127" t="str">
+        <f>FUNDAMENTALS!I26</f>
+        <v>Weighted Russian Twist</v>
+      </c>
+      <c r="D46" s="128" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E46" s="128">
+        <v>12</v>
+      </c>
+      <c r="F46" s="128" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G46" s="128"/>
+      <c r="H46" s="127" t="str">
+        <f>FUNDAMENTALS!H26</f>
+        <v>Half-Kneeling Rotation</v>
+      </c>
+      <c r="I46" s="127" t="str">
+        <f>FUNDAMENTALS!J26</f>
+        <v>Kettlebell Figure-8</v>
+      </c>
+      <c r="J46" s="129" t="s">
+        <v>2350</v>
+      </c>
+      <c r="K46" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A47" s="126">
+        <v>2</v>
+      </c>
+      <c r="B47" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C47" s="127" t="str">
+        <f>FUNDAMENTALS!E19</f>
+        <v>Farmer's Carry (no straps)</v>
+      </c>
+      <c r="D47" s="128" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E47" s="128" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F47" s="128" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G47" s="128"/>
+      <c r="H47" s="130" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I47" s="130" t="str">
+        <f>FUNDAMENTALS!F19</f>
+        <v>Suitcase Carry</v>
+      </c>
+      <c r="J47" s="129" t="s">
+        <v>2355</v>
+      </c>
+      <c r="K47" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="119"/>
+      <c r="B48" s="119" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C48" s="119"/>
+      <c r="D48" s="120"/>
+      <c r="E48" s="120"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="120">
+        <f>SUM(G37:G45)</f>
+        <v>38</v>
+      </c>
+      <c r="H48" s="119"/>
+      <c r="I48" s="119"/>
+      <c r="J48" s="121"/>
+      <c r="K48" s="119"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="115"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="115"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="122"/>
+      <c r="F49" s="122"/>
+      <c r="G49" s="122"/>
+      <c r="H49" s="115"/>
+      <c r="I49" s="115"/>
+      <c r="J49" s="118"/>
+      <c r="K49" s="115"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="112" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B50" s="112"/>
+      <c r="C50" s="112"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="112"/>
+      <c r="I50" s="112"/>
+      <c r="J50" s="114"/>
+      <c r="K50" s="112"/>
+    </row>
+    <row r="51" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A51" s="115">
+        <v>3</v>
+      </c>
+      <c r="B51" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C51" s="116" t="str">
+        <f>FUNDAMENTALS!G11</f>
+        <v>Prying Goblet Squat</v>
+      </c>
+      <c r="D51" s="117">
+        <v>1</v>
+      </c>
+      <c r="E51" s="117" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F51" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G51" s="117">
+        <v>5</v>
+      </c>
+      <c r="H51" s="116"/>
+      <c r="I51" s="116"/>
+      <c r="J51" s="118" t="s">
+        <v>2285</v>
+      </c>
+      <c r="K51" s="115"/>
+    </row>
+    <row r="52" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="115">
+        <v>3</v>
+      </c>
+      <c r="B52" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C52" s="116" t="str">
+        <f>FUNDAMENTALS!F11</f>
+        <v>Banded Lateral Walks</v>
+      </c>
+      <c r="D52" s="117">
+        <v>1</v>
+      </c>
+      <c r="E52" s="117" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F52" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G52" s="117"/>
+      <c r="H52" s="116"/>
+      <c r="I52" s="116"/>
+      <c r="J52" s="118" t="s">
+        <v>2286</v>
+      </c>
+      <c r="K52" s="115"/>
+    </row>
+    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="115">
+        <v>3</v>
+      </c>
+      <c r="B53" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C53" s="116" t="str">
+        <f>FUNDAMENTALS!D26</f>
+        <v>Thoracic Rotations</v>
+      </c>
+      <c r="D53" s="117">
+        <v>1</v>
+      </c>
+      <c r="E53" s="117" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F53" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G53" s="117"/>
+      <c r="H53" s="116"/>
+      <c r="I53" s="116"/>
+      <c r="J53" s="118" t="s">
+        <v>2287</v>
+      </c>
+      <c r="K53" s="115"/>
+    </row>
+    <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A54" s="115">
+        <v>3</v>
+      </c>
+      <c r="B54" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C54" s="116" t="str">
+        <f>FUNDAMENTALS!N26</f>
+        <v>Rotational Medicine Ball Throw</v>
+      </c>
+      <c r="D54" s="117">
+        <v>3</v>
+      </c>
+      <c r="E54" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F54" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G54" s="117">
+        <v>5</v>
+      </c>
+      <c r="H54" s="116"/>
+      <c r="I54" s="116"/>
+      <c r="J54" s="118" t="s">
+        <v>2288</v>
+      </c>
+      <c r="K54" s="115"/>
+    </row>
+    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="115">
+        <v>3</v>
+      </c>
+      <c r="B55" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C55" s="116" t="str">
+        <f>FUNDAMENTALS!I11</f>
+        <v>Cossack Squat</v>
+      </c>
+      <c r="D55" s="117">
+        <v>3</v>
+      </c>
+      <c r="E55" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F55" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G55" s="117">
+        <v>11</v>
+      </c>
+      <c r="H55" s="116" t="str">
+        <f>FUNDAMENTALS!H11</f>
+        <v>Kettlebell Cossack Squat</v>
+      </c>
+      <c r="I55" s="116" t="str">
+        <f>FUNDAMENTALS!J11</f>
+        <v>Goblet Lateral Lunge</v>
+      </c>
+      <c r="J55" s="118" t="s">
+        <v>2289</v>
+      </c>
+      <c r="K55" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="115">
+        <v>3</v>
+      </c>
+      <c r="B56" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C56" s="116" t="str">
+        <f>FUNDAMENTALS!I16</f>
+        <v>Dip</v>
+      </c>
+      <c r="D56" s="117">
+        <v>3</v>
+      </c>
+      <c r="E56" s="117" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F56" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G56" s="117"/>
+      <c r="H56" s="116" t="str">
+        <f>FUNDAMENTALS!H16</f>
+        <v>Banded Dip</v>
+      </c>
+      <c r="I56" s="116" t="str">
+        <f>FUNDAMENTALS!J16</f>
+        <v>Ring Dip</v>
+      </c>
+      <c r="J56" s="118" t="s">
+        <v>2290</v>
+      </c>
+      <c r="K56" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="115">
+        <v>3</v>
+      </c>
+      <c r="B57" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C57" s="116" t="str">
+        <f>FUNDAMENTALS!I12</f>
+        <v>Reverse Nordic Curl</v>
+      </c>
+      <c r="D57" s="117">
+        <v>3</v>
+      </c>
+      <c r="E57" s="117">
+        <v>8</v>
+      </c>
+      <c r="F57" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G57" s="117">
+        <v>9</v>
+      </c>
+      <c r="H57" s="116" t="str">
+        <f>FUNDAMENTALS!H12</f>
+        <v>Assisted Reverse Nordic Curl</v>
+      </c>
+      <c r="I57" s="116" t="str">
+        <f>FUNDAMENTALS!J12</f>
+        <v>Sissy Squat</v>
+      </c>
+      <c r="J57" s="118" t="s">
+        <v>2291</v>
+      </c>
+      <c r="K57" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A58" s="115">
+        <v>3</v>
+      </c>
+      <c r="B58" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C58" s="116" t="str">
+        <f>FUNDAMENTALS!I20</f>
+        <v>Wide Inverted Row</v>
+      </c>
+      <c r="D58" s="117">
+        <v>3</v>
+      </c>
+      <c r="E58" s="117">
+        <v>12</v>
+      </c>
+      <c r="F58" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G58" s="117"/>
+      <c r="H58" s="116" t="str">
+        <f>FUNDAMENTALS!H20</f>
+        <v>Australian Pull-Up</v>
+      </c>
+      <c r="I58" s="116" t="str">
+        <f>FUNDAMENTALS!J20</f>
+        <v>Feet-Elevated Ring Row</v>
+      </c>
+      <c r="J58" s="118" t="s">
+        <v>2292</v>
+      </c>
+      <c r="K58" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A59" s="126">
+        <v>3</v>
+      </c>
+      <c r="B59" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C59" s="127" t="str">
+        <f>FUNDAMENTALS!J24</f>
+        <v>Hollow Rock</v>
+      </c>
+      <c r="D59" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E59" s="128">
+        <v>12</v>
+      </c>
+      <c r="F59" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G59" s="128">
+        <v>8</v>
+      </c>
+      <c r="H59" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="I59" s="127" t="str">
+        <f>FUNDAMENTALS!K24</f>
+        <v>Squeeze-Loaded Hollow Hold</v>
+      </c>
+      <c r="J59" s="129" t="s">
+        <v>2357</v>
+      </c>
+      <c r="K59" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A60" s="126">
+        <v>3</v>
+      </c>
+      <c r="B60" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C60" s="127" t="str">
+        <f>FUNDAMENTALS!J25</f>
+        <v>Side Plank Hip Dip</v>
+      </c>
+      <c r="D60" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E60" s="128" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F60" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G60" s="128"/>
+      <c r="H60" s="127" t="str">
+        <f>FUNDAMENTALS!I25</f>
+        <v>Side Plank</v>
+      </c>
+      <c r="I60" s="127" t="str">
+        <f>FUNDAMENTALS!K25</f>
+        <v>Star Side Plank</v>
+      </c>
+      <c r="J60" s="129" t="s">
+        <v>2358</v>
+      </c>
+      <c r="K60" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A61" s="126">
+        <v>3</v>
+      </c>
+      <c r="B61" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C61" s="130" t="str">
+        <f>FUNDAMENTALS!J6</f>
+        <v>Kettlebell Swing</v>
+      </c>
+      <c r="D61" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E61" s="128">
+        <v>15</v>
+      </c>
+      <c r="F61" s="128" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G61" s="128"/>
+      <c r="H61" s="130" t="s">
+        <v>2359</v>
+      </c>
+      <c r="I61" s="130" t="s">
+        <v>2360</v>
+      </c>
+      <c r="J61" s="129" t="s">
+        <v>2361</v>
+      </c>
+      <c r="K61" s="126" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="119"/>
+      <c r="B62" s="119" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C62" s="119"/>
+      <c r="D62" s="120"/>
+      <c r="E62" s="120"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="120">
+        <f>SUM(G51:G59)</f>
+        <v>38</v>
+      </c>
+      <c r="H62" s="119"/>
+      <c r="I62" s="119"/>
+      <c r="J62" s="121"/>
+      <c r="K62" s="119"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="115"/>
+      <c r="B63" s="115"/>
+      <c r="C63" s="115"/>
+      <c r="D63" s="122"/>
+      <c r="E63" s="122"/>
+      <c r="F63" s="122"/>
+      <c r="G63" s="122"/>
+      <c r="H63" s="115"/>
+      <c r="I63" s="115"/>
+      <c r="J63" s="118"/>
+      <c r="K63" s="115"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="112" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B64" s="112"/>
+      <c r="C64" s="112"/>
+      <c r="D64" s="113"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="113"/>
+      <c r="G64" s="113"/>
+      <c r="H64" s="112"/>
+      <c r="I64" s="112"/>
+      <c r="J64" s="114"/>
+      <c r="K64" s="112"/>
+    </row>
+    <row r="65" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="115">
+        <v>4</v>
+      </c>
+      <c r="B65" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C65" s="116" t="s">
+        <v>360</v>
+      </c>
+      <c r="D65" s="117">
+        <v>1</v>
+      </c>
+      <c r="E65" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F65" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G65" s="117">
+        <v>5</v>
+      </c>
+      <c r="H65" s="116"/>
+      <c r="I65" s="116"/>
+      <c r="J65" s="118" t="s">
+        <v>2295</v>
+      </c>
+      <c r="K65" s="115"/>
+    </row>
+    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="115">
+        <v>4</v>
+      </c>
+      <c r="B66" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C66" s="116" t="str">
+        <f>FUNDAMENTALS!E26</f>
+        <v>90/90 Hip Switches</v>
+      </c>
+      <c r="D66" s="117">
+        <v>1</v>
+      </c>
+      <c r="E66" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F66" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G66" s="117"/>
+      <c r="H66" s="116"/>
+      <c r="I66" s="116"/>
+      <c r="J66" s="118" t="s">
+        <v>2296</v>
+      </c>
+      <c r="K66" s="115"/>
+    </row>
+    <row r="67" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="115">
+        <v>4</v>
+      </c>
+      <c r="B67" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C67" s="116" t="str">
+        <f>FUNDAMENTALS!E21</f>
+        <v>Scapular Pull-ups</v>
+      </c>
+      <c r="D67" s="117">
+        <v>1</v>
+      </c>
+      <c r="E67" s="117">
+        <v>8</v>
+      </c>
+      <c r="F67" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G67" s="117"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="116"/>
+      <c r="J67" s="118" t="s">
+        <v>2297</v>
+      </c>
+      <c r="K67" s="115"/>
+    </row>
+    <row r="68" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A68" s="115">
+        <v>4</v>
+      </c>
+      <c r="B68" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C68" s="116" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D68" s="117">
+        <v>5</v>
+      </c>
+      <c r="E68" s="117">
+        <v>3</v>
+      </c>
+      <c r="F68" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G68" s="117">
+        <v>5</v>
+      </c>
+      <c r="H68" s="116"/>
+      <c r="I68" s="116"/>
+      <c r="J68" s="118" t="s">
+        <v>2299</v>
+      </c>
+      <c r="K68" s="115"/>
+    </row>
+    <row r="69" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A69" s="115">
+        <v>4</v>
+      </c>
+      <c r="B69" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C69" s="116" t="str">
+        <f>FUNDAMENTALS!I10</f>
+        <v>Nordic Curl</v>
+      </c>
+      <c r="D69" s="117">
+        <v>3</v>
+      </c>
+      <c r="E69" s="117">
+        <v>5</v>
+      </c>
+      <c r="F69" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G69" s="117">
+        <v>11</v>
+      </c>
+      <c r="H69" s="116" t="str">
+        <f>FUNDAMENTALS!H10</f>
+        <v>Sliding Hamstring Curl</v>
+      </c>
+      <c r="I69" s="116" t="s">
+        <v>2300</v>
+      </c>
+      <c r="J69" s="118" t="s">
+        <v>2301</v>
+      </c>
+      <c r="K69" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A70" s="115">
+        <v>4</v>
+      </c>
+      <c r="B70" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C70" s="116" t="str">
+        <f>FUNDAMENTALS!I17</f>
+        <v>Wall Handstand</v>
+      </c>
+      <c r="D70" s="117">
+        <v>3</v>
+      </c>
+      <c r="E70" s="117" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F70" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G70" s="117"/>
+      <c r="H70" s="116" t="str">
+        <f>FUNDAMENTALS!H17</f>
+        <v>Wall Walk</v>
+      </c>
+      <c r="I70" s="116" t="str">
+        <f>FUNDAMENTALS!J17</f>
+        <v>Back-to-Wall Handstand Hold</v>
+      </c>
+      <c r="J70" s="118" t="s">
+        <v>2303</v>
+      </c>
+      <c r="K70" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A71" s="115">
+        <v>4</v>
+      </c>
+      <c r="B71" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C71" s="116" t="str">
+        <f>FUNDAMENTALS!I9</f>
+        <v>Wall Sit</v>
+      </c>
+      <c r="D71" s="117">
+        <v>3</v>
+      </c>
+      <c r="E71" s="117" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F71" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G71" s="117">
+        <v>9</v>
+      </c>
+      <c r="H71" s="116" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I71" s="116" t="str">
+        <f>FUNDAMENTALS!J9</f>
+        <v>Horse Stance</v>
+      </c>
+      <c r="J71" s="118" t="s">
+        <v>2306</v>
+      </c>
+      <c r="K71" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A72" s="115">
+        <v>4</v>
+      </c>
+      <c r="B72" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C72" s="116" t="str">
+        <f>FUNDAMENTALS!I19</f>
+        <v>Dead Hang</v>
+      </c>
+      <c r="D72" s="117">
+        <v>3</v>
+      </c>
+      <c r="E72" s="117" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F72" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G72" s="117"/>
+      <c r="H72" s="116" t="str">
+        <f>FUNDAMENTALS!H19</f>
+        <v>Active Hang</v>
+      </c>
+      <c r="I72" s="116" t="str">
+        <f>FUNDAMENTALS!J19</f>
+        <v>Towel Hang</v>
+      </c>
+      <c r="J72" s="118" t="s">
+        <v>2307</v>
+      </c>
+      <c r="K72" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A73" s="126">
+        <v>4</v>
+      </c>
+      <c r="B73" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C73" s="127" t="str">
+        <f>FUNDAMENTALS!I28</f>
+        <v>Hanging Leg Raise</v>
+      </c>
+      <c r="D73" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E73" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F73" s="128" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G73" s="128">
+        <v>8</v>
+      </c>
+      <c r="H73" s="127" t="str">
+        <f>FUNDAMENTALS!H28</f>
+        <v>Hanging Knee Raise</v>
+      </c>
+      <c r="I73" s="127" t="str">
+        <f>FUNDAMENTALS!J28</f>
+        <v>Toes-to-Bar</v>
+      </c>
+      <c r="J73" s="129" t="s">
+        <v>2365</v>
+      </c>
+      <c r="K73" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A74" s="126">
+        <v>4</v>
+      </c>
+      <c r="B74" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C74" s="127" t="str">
+        <f>FUNDAMENTALS!F29</f>
+        <v>Dragon Flag (Tuck)</v>
+      </c>
+      <c r="D74" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E74" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F74" s="128" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G74" s="128"/>
+      <c r="H74" s="127" t="str">
+        <f>FUNDAMENTALS!E29</f>
+        <v>Dragon Flag Candlestick</v>
+      </c>
+      <c r="I74" s="127" t="str">
+        <f>FUNDAMENTALS!G29</f>
+        <v>Tuck Dragon Flag Hold</v>
+      </c>
+      <c r="J74" s="129" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K74" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A75" s="126">
+        <v>4</v>
+      </c>
+      <c r="B75" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C75" s="127" t="str">
+        <f>FUNDAMENTALS!H24</f>
+        <v>Forearm Plank</v>
+      </c>
+      <c r="D75" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E75" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F75" s="128" t="s">
+        <v>2367</v>
+      </c>
+      <c r="G75" s="128"/>
+      <c r="H75" s="130" t="s">
+        <v>2368</v>
+      </c>
+      <c r="I75" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="J75" s="129" t="s">
+        <v>2369</v>
+      </c>
+      <c r="K75" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="119"/>
+      <c r="B76" s="119" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C76" s="119"/>
+      <c r="D76" s="120"/>
+      <c r="E76" s="120"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="120">
+        <f>SUM(G65:G73)</f>
+        <v>38</v>
+      </c>
+      <c r="H76" s="119"/>
+      <c r="I76" s="119"/>
+      <c r="J76" s="121"/>
+      <c r="K76" s="119"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" s="115"/>
+      <c r="B77" s="115"/>
+      <c r="C77" s="115"/>
+      <c r="D77" s="115"/>
+      <c r="E77" s="115"/>
+      <c r="F77" s="115"/>
+      <c r="G77" s="115"/>
+      <c r="H77" s="115"/>
+      <c r="I77" s="115"/>
+      <c r="J77" s="118"/>
+      <c r="K77" s="115"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="123" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B78" s="115"/>
+      <c r="C78" s="115"/>
+      <c r="D78" s="115"/>
+      <c r="E78" s="115"/>
+      <c r="F78" s="115"/>
+      <c r="G78" s="115"/>
+      <c r="H78" s="115"/>
+      <c r="I78" s="115"/>
+      <c r="J78" s="118"/>
+      <c r="K78" s="115"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A79" s="115"/>
+      <c r="B79" s="124" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C79" s="124" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D79" s="124" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E79" s="115"/>
+      <c r="F79" s="115"/>
+      <c r="G79" s="115"/>
+      <c r="H79" s="115"/>
+      <c r="I79" s="115"/>
+      <c r="J79" s="118"/>
+      <c r="K79" s="115"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A80" s="115"/>
+      <c r="B80" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="115">
+        <f>COUNTIF($K$23:$K$75,$B80)</f>
+        <v>8</v>
+      </c>
+      <c r="D80" s="125">
+        <f>C80/($C$80+$C$81)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="115"/>
+      <c r="F80" s="115"/>
+      <c r="G80" s="115"/>
+      <c r="H80" s="115"/>
+      <c r="I80" s="115"/>
+      <c r="J80" s="118"/>
+      <c r="K80" s="115"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A81" s="115"/>
+      <c r="B81" s="115" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C81" s="115">
+        <f>COUNTIF($K$23:$K$75,$B81)</f>
+        <v>8</v>
+      </c>
+      <c r="D81" s="125">
+        <f>C81/($C$80+$C$81)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E81" s="115"/>
+      <c r="F81" s="115"/>
+      <c r="G81" s="115"/>
+      <c r="H81" s="115"/>
+      <c r="I81" s="115"/>
+      <c r="J81" s="118"/>
+      <c r="K81" s="115"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="115"/>
+      <c r="B82" s="115" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C82" s="115">
+        <f>COUNTIF($K$23:$K$75,"Core")</f>
+        <v>10</v>
+      </c>
+      <c r="D82" s="115" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E82" s="115"/>
+      <c r="F82" s="115"/>
+      <c r="G82" s="115"/>
+      <c r="H82" s="115"/>
+      <c r="I82" s="115"/>
+      <c r="J82" s="118"/>
+      <c r="K82" s="115"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A83" s="115"/>
+      <c r="B83" s="115" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C83" s="115">
+        <f>COUNTIF($K$23:$K$75,"Cond")</f>
+        <v>2</v>
+      </c>
+      <c r="D83" s="115" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E83" s="115"/>
+      <c r="F83" s="115"/>
+      <c r="G83" s="115"/>
+      <c r="H83" s="115"/>
+      <c r="I83" s="115"/>
+      <c r="J83" s="118"/>
+      <c r="K83" s="115"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A84" s="115"/>
+      <c r="B84" s="123" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C84" s="123">
+        <f>G34+G48+G62+G76</f>
+        <v>152</v>
+      </c>
+      <c r="D84" s="115" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E84" s="115"/>
+      <c r="F84" s="115"/>
+      <c r="G84" s="115"/>
+      <c r="H84" s="115"/>
+      <c r="I84" s="115"/>
+      <c r="J84" s="118"/>
+      <c r="K84" s="115"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" s="115"/>
+      <c r="B85" s="115" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C85" s="115"/>
+      <c r="D85" s="115" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E85" s="115"/>
+      <c r="F85" s="115"/>
+      <c r="G85" s="115"/>
+      <c r="H85" s="115"/>
+      <c r="I85" s="115"/>
+      <c r="J85" s="118"/>
+      <c r="K85" s="115"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A86" s="115"/>
+      <c r="B86" s="115" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C86" s="115"/>
+      <c r="D86" s="115" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E86" s="115"/>
+      <c r="F86" s="115"/>
+      <c r="G86" s="115"/>
+      <c r="H86" s="115"/>
+      <c r="I86" s="115"/>
+      <c r="J86" s="118"/>
+      <c r="K86" s="115"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A87" s="115"/>
+      <c r="B87" s="115" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C87" s="115"/>
+      <c r="D87" s="115" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E87" s="115"/>
+      <c r="F87" s="115"/>
+      <c r="G87" s="115"/>
+      <c r="H87" s="115"/>
+      <c r="I87" s="115"/>
+      <c r="J87" s="118"/>
+      <c r="K87" s="115"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B88" s="115" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D88" s="115" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A89" s="102" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B90" s="124" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C90" s="105" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B91" s="115" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C91" s="118" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B92" s="115" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C92" s="118" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B93" s="115" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C93" s="118" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B94" s="115" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C94" s="118" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="B95" s="115" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C95" s="118" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4012A2FE-2E88-2345-BAC5-0FBF199696AF}">
+  <dimension ref="A1:V76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="7" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="46" customWidth="1"/>
+    <col min="19" max="19" width="30" customWidth="1"/>
+    <col min="20" max="20" width="46" customWidth="1"/>
+    <col min="21" max="22" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A1" s="99" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+    </row>
+    <row r="3" spans="1:22" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="U3" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="V3" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="60" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+    </row>
+    <row r="5" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="25">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="25">
+        <f t="shared" ref="P5:P12" si="0">COUNTA(D5:N5)-COUNTIF(D5:N5,"no honest gym equivalent")</f>
+        <v>4</v>
+      </c>
+      <c r="T5" s="35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="25">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="66" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G6" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="K6" s="67" t="s">
+        <v>117</v>
+      </c>
+      <c r="L6" s="67" t="s">
+        <v>420</v>
+      </c>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="25">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="T6" s="35" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="62" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="25">
+        <v>1</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="25">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="25">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="25">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="T8" s="35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="62" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C9" s="25">
+        <v>1</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="65" t="s">
+        <v>364</v>
+      </c>
+      <c r="I9" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="87">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T9" s="35" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="25">
+        <v>2</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="66" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G10" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="25">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="25">
+        <v>2</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="G11" s="68" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H11" s="68" t="s">
+        <v>1846</v>
+      </c>
+      <c r="I11" s="70" t="s">
+        <v>1915</v>
+      </c>
+      <c r="J11" s="69" t="s">
+        <v>319</v>
+      </c>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="76" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B12" s="72" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C12" s="80">
+        <v>2</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="F12" s="78" t="s">
+        <v>2051</v>
+      </c>
+      <c r="G12" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="77" t="s">
+        <v>2060</v>
+      </c>
+      <c r="I12" s="79" t="s">
+        <v>2057</v>
+      </c>
+      <c r="J12" s="69" t="s">
+        <v>2055</v>
+      </c>
+      <c r="P12" s="84">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="61" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+    </row>
+    <row r="14" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="25">
+        <v>1</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="25">
+        <f>COUNTA(D14:N14)-COUNTIF(D14:N14,"no honest gym equivalent")</f>
+        <v>4</v>
+      </c>
+      <c r="T14" s="35" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C15" s="25">
+        <v>1</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="25">
+        <f>COUNTA(D15:N15)-COUNTIF(D15:N15,"no honest gym equivalent")</f>
+        <v>4</v>
+      </c>
+      <c r="T15" s="35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="25">
+        <v>2</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="25">
+        <f>COUNTA(D16:N16)-COUNTIF(D16:N16,"no honest gym equivalent")</f>
+        <v>4</v>
+      </c>
+      <c r="T16" s="35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="25">
+        <v>2</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32">
+        <f>COUNTA(D17:N17)-COUNTIF(D17:N17,"no honest gym equivalent")</f>
+        <v>0</v>
+      </c>
+      <c r="T17" s="35" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="61" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+    </row>
+    <row r="19" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="62" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="25">
+        <v>1</v>
+      </c>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="67" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K19" s="67" t="s">
+        <v>1684</v>
+      </c>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="25">
+        <f>COUNTA(D19:N19)-COUNTIF(D19:N19,"no honest gym equivalent")</f>
+        <v>5</v>
+      </c>
+      <c r="T19" s="35" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="25">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="J20" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="25">
+        <f>COUNTA(D20:N20)-COUNTIF(D20:N20,"no honest gym equivalent")</f>
+        <v>5</v>
+      </c>
+      <c r="T20" s="35" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="C21" s="25">
+        <v>2</v>
+      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="25">
+        <f>COUNTA(D21:N21)-COUNTIF(D21:N21,"no honest gym equivalent")</f>
+        <v>3</v>
+      </c>
+      <c r="T21" s="35" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" s="25">
+        <v>3</v>
+      </c>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="66" t="s">
+        <v>553</v>
+      </c>
+      <c r="H22" s="66" t="s">
+        <v>264</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="J22" s="67" t="s">
+        <v>1939</v>
+      </c>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="25">
+        <f>COUNTA(D22:N22)-COUNTIF(D22:N22,"no honest gym equivalent")</f>
+        <v>4</v>
+      </c>
+      <c r="T22" s="35" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="61" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+    </row>
+    <row r="24" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C24" s="25">
+        <v>1</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="25">
+        <f t="shared" ref="P24:P30" si="1">COUNTA(D24:N24)-COUNTIF(D24:N24,"no honest gym equivalent")</f>
+        <v>2</v>
+      </c>
+      <c r="T24" s="35" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="62" t="s">
+        <v>305</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="25">
+        <v>1</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="I25" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="25">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T25" s="35" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="62" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="C26" s="25">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="66" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H26" s="66" t="s">
+        <v>317</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="J26" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>320</v>
+      </c>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="25">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="T26" s="35" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" s="25">
+        <v>1</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="I27" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="25">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T27" s="35" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="62" t="s">
+        <v>298</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="C28" s="25">
+        <v>2</v>
+      </c>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="25">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T28" s="35" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C29" s="25">
+        <v>3</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="35" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="62" t="s">
+        <v>288</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" s="25">
+        <v>3</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="35" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="U5:U12 U14:U17 U19:U22 U24:U30" xr:uid="{DCE8C963-AD8A-FC4F-A79C-C395C8540AEB}">
+      <formula1>"keep,change,discuss"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7653,13 +11827,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -8141,7 +12315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8162,30 +12336,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="99" t="s">
         <v>2165</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="100"/>
+      <c r="V1" s="100"/>
     </row>
     <row r="3" spans="1:22" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="20" t="s">
@@ -8240,30 +12414,30 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="60" t="s">
         <v>2162</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
     </row>
     <row r="5" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
@@ -8275,36 +12449,36 @@
       <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="66" t="s">
+      <c r="D5" s="26"/>
+      <c r="E5" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="66" t="s">
+      <c r="F5" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="66" t="s">
+      <c r="G5" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="66" t="s">
+      <c r="H5" s="63" t="s">
         <v>101</v>
       </c>
       <c r="I5" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="K5" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
       <c r="O5" s="24" t="s">
         <v>103</v>
       </c>
       <c r="P5" s="25">
-        <f>COUNTA(D5:N5)</f>
+        <f t="shared" ref="P5:P12" si="0">COUNTA(D5:N5)</f>
         <v>7</v>
       </c>
       <c r="Q5" s="30" t="s">
@@ -8332,40 +12506,40 @@
       <c r="C6" s="25">
         <v>1</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="66" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="63" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="63" t="s">
         <v>113</v>
       </c>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="63" t="s">
         <v>114</v>
       </c>
       <c r="I6" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="J6" s="67" t="s">
+      <c r="J6" s="64" t="s">
         <v>350</v>
       </c>
-      <c r="K6" s="67" t="s">
+      <c r="K6" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="L6" s="67" t="s">
+      <c r="L6" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="M6" s="67" t="s">
+      <c r="M6" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="N6" s="65"/>
+      <c r="N6" s="26"/>
       <c r="O6" s="24" t="s">
         <v>103</v>
       </c>
       <c r="P6" s="25">
-        <f>COUNTA(D6:N6)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="Q6" s="30" t="s">
@@ -8420,7 +12594,7 @@
         <v>103</v>
       </c>
       <c r="P7" s="25">
-        <f>COUNTA(D7:N7)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="Q7" s="30" t="s">
@@ -8448,42 +12622,42 @@
       <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="66" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="63" t="s">
         <v>137</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="66" t="s">
+      <c r="G8" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="H8" s="66" t="s">
+      <c r="H8" s="63" t="s">
         <v>1860</v>
       </c>
       <c r="I8" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="J8" s="67" t="s">
+      <c r="J8" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="K8" s="104" t="s">
+      <c r="K8" s="97" t="s">
         <v>2196</v>
       </c>
-      <c r="L8" s="70" t="s">
+      <c r="L8" s="67" t="s">
         <v>134</v>
       </c>
-      <c r="M8" s="70" t="s">
+      <c r="M8" s="67" t="s">
         <v>135</v>
       </c>
-      <c r="N8" s="70" t="s">
+      <c r="N8" s="67" t="s">
         <v>136</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>103</v>
       </c>
       <c r="P8" s="25">
-        <f>COUNTA(D8:N8)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q8" s="30" t="s">
@@ -8493,7 +12667,7 @@
         <v>2172</v>
       </c>
       <c r="S8" s="31"/>
-      <c r="T8" s="89" t="s">
+      <c r="T8" s="83" t="s">
         <v>2197</v>
       </c>
       <c r="U8" s="17"/>
@@ -8508,33 +12682,33 @@
       <c r="B9" s="24" t="s">
         <v>2186</v>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="91" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="85" t="s">
         <v>1195</v>
       </c>
-      <c r="J9" s="67" t="s">
+      <c r="J9" s="64" t="s">
         <v>1208</v>
       </c>
-      <c r="K9" s="67" t="s">
+      <c r="K9" s="64" t="s">
         <v>364</v>
       </c>
-      <c r="L9" s="67" t="s">
+      <c r="L9" s="64" t="s">
         <v>99</v>
       </c>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
       <c r="O9" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="P9" s="94">
-        <f>COUNTA(D9:N9)</f>
+      <c r="P9" s="87">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q9" s="30" t="s">
@@ -8544,7 +12718,7 @@
         <v>2188</v>
       </c>
       <c r="S9" s="31"/>
-      <c r="T9" s="89" t="s">
+      <c r="T9" s="83" t="s">
         <v>2189</v>
       </c>
       <c r="U9" s="17"/>
@@ -8562,30 +12736,30 @@
       <c r="C10" s="25">
         <v>2</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="63" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="66" t="s">
+      <c r="G10" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="H10" s="66" t="s">
+      <c r="H10" s="63" t="s">
         <v>142</v>
       </c>
       <c r="I10" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="65"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
       <c r="O10" s="24" t="s">
         <v>103</v>
       </c>
       <c r="P10" s="25">
-        <f>COUNTA(D10:N10)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="Q10" s="30" t="s">
@@ -8613,36 +12787,36 @@
       <c r="C11" s="25">
         <v>2</v>
       </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="66" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="F11" s="66" t="s">
+      <c r="F11" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="G11" s="66" t="s">
+      <c r="G11" s="63" t="s">
         <v>1616</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="63" t="s">
         <v>1915</v>
       </c>
       <c r="I11" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="J11" s="67" t="s">
+      <c r="J11" s="64" t="s">
         <v>1846</v>
       </c>
-      <c r="K11" s="67" t="s">
+      <c r="K11" s="64" t="s">
         <v>319</v>
       </c>
-      <c r="L11" s="65"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="65"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
       <c r="O11" s="24" t="s">
         <v>151</v>
       </c>
       <c r="P11" s="25">
-        <f>COUNTA(D11:N11)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Q11" s="30" t="s">
@@ -8661,89 +12835,89 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="71" t="s">
         <v>2192</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="72" t="s">
         <v>2181</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="80">
         <v>2</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="88" t="s">
         <v>691</v>
       </c>
-      <c r="E12" s="95" t="s">
+      <c r="E12" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="95" t="s">
+      <c r="F12" s="88" t="s">
         <v>1216</v>
       </c>
-      <c r="G12" s="95" t="s">
+      <c r="G12" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="95" t="s">
+      <c r="H12" s="88" t="s">
         <v>548</v>
       </c>
-      <c r="I12" s="96" t="s">
+      <c r="I12" s="89" t="s">
         <v>2192</v>
       </c>
-      <c r="J12" s="97" t="s">
+      <c r="J12" s="90" t="s">
         <v>1213</v>
       </c>
-      <c r="K12" s="103" t="s">
+      <c r="K12" s="96" t="s">
         <v>2195</v>
       </c>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="77" t="s">
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="P12" s="87">
-        <f>COUNTA(D12:N12)</f>
+      <c r="P12" s="81">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="Q12" s="78" t="s">
+      <c r="Q12" s="73" t="s">
         <v>2182</v>
       </c>
-      <c r="R12" s="78" t="s">
+      <c r="R12" s="73" t="s">
         <v>2183</v>
       </c>
-      <c r="S12" s="79"/>
-      <c r="T12" s="88" t="s">
+      <c r="S12" s="74"/>
+      <c r="T12" s="82" t="s">
         <v>2198</v>
       </c>
-      <c r="U12" s="81"/>
-      <c r="V12" s="81" t="s">
+      <c r="U12" s="75"/>
+      <c r="V12" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="61" t="s">
         <v>2163</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="60"/>
+      <c r="P13" s="60"/>
+      <c r="Q13" s="60"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="60"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
     </row>
     <row r="14" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="23" t="s">
@@ -8976,30 +13150,30 @@
       </c>
     </row>
     <row r="18" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63" t="s">
+      <c r="A18" s="61" t="s">
         <v>2164</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="62"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="62"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="60"/>
+      <c r="P18" s="60"/>
+      <c r="Q18" s="60"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="60"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
     </row>
     <row r="19" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="23" t="s">
@@ -9011,31 +13185,31 @@
       <c r="C19" s="25">
         <v>1</v>
       </c>
-      <c r="D19" s="99"/>
-      <c r="E19" s="100" t="s">
+      <c r="D19" s="92"/>
+      <c r="E19" s="93" t="s">
         <v>253</v>
       </c>
-      <c r="F19" s="100" t="s">
+      <c r="F19" s="93" t="s">
         <v>313</v>
       </c>
-      <c r="G19" s="100" t="s">
+      <c r="G19" s="93" t="s">
         <v>1670</v>
       </c>
-      <c r="H19" s="100" t="s">
+      <c r="H19" s="93" t="s">
         <v>248</v>
       </c>
-      <c r="I19" s="101" t="s">
+      <c r="I19" s="94" t="s">
         <v>232</v>
       </c>
-      <c r="J19" s="70" t="s">
+      <c r="J19" s="67" t="s">
         <v>249</v>
       </c>
-      <c r="K19" s="70" t="s">
+      <c r="K19" s="67" t="s">
         <v>1384</v>
       </c>
-      <c r="L19" s="99"/>
-      <c r="M19" s="99"/>
-      <c r="N19" s="99"/>
+      <c r="L19" s="92"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="92"/>
       <c r="O19" s="24" t="s">
         <v>103</v>
       </c>
@@ -9050,7 +13224,7 @@
         <v>2193</v>
       </c>
       <c r="S19" s="31"/>
-      <c r="T19" s="102" t="s">
+      <c r="T19" s="95" t="s">
         <v>2194</v>
       </c>
       <c r="U19" s="17"/>
@@ -9184,35 +13358,35 @@
       <c r="C22" s="25">
         <v>3</v>
       </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="66" t="s">
+      <c r="D22" s="26"/>
+      <c r="E22" s="63" t="s">
         <v>1236</v>
       </c>
-      <c r="F22" s="66" t="s">
+      <c r="F22" s="63" t="s">
         <v>257</v>
       </c>
-      <c r="G22" s="66" t="s">
+      <c r="G22" s="63" t="s">
         <v>259</v>
       </c>
-      <c r="H22" s="66" t="s">
+      <c r="H22" s="63" t="s">
         <v>258</v>
       </c>
       <c r="I22" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="J22" s="67" t="s">
+      <c r="J22" s="64" t="s">
         <v>1231</v>
       </c>
-      <c r="K22" s="67" t="s">
+      <c r="K22" s="64" t="s">
         <v>260</v>
       </c>
-      <c r="L22" s="67" t="s">
+      <c r="L22" s="64" t="s">
         <v>1243</v>
       </c>
-      <c r="M22" s="67" t="s">
+      <c r="M22" s="64" t="s">
         <v>1260</v>
       </c>
-      <c r="N22" s="67" t="s">
+      <c r="N22" s="64" t="s">
         <v>261</v>
       </c>
       <c r="O22" s="38" t="s">
@@ -9238,30 +13412,30 @@
       </c>
     </row>
     <row r="23" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="61" t="s">
         <v>2120</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="60"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="60"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="60"/>
+      <c r="S23" s="60"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
     </row>
     <row r="24" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="23" t="s">
@@ -9304,7 +13478,7 @@
         <v>103</v>
       </c>
       <c r="P24" s="25">
-        <f>COUNTA(D24:N24)</f>
+        <f t="shared" ref="P24:P30" si="1">COUNTA(D24:N24)</f>
         <v>8</v>
       </c>
       <c r="Q24" s="30" t="s">
@@ -9355,7 +13529,7 @@
         <v>103</v>
       </c>
       <c r="P25" s="25">
-        <f>COUNTA(D25:N25)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q25" s="30" t="s">
@@ -9381,44 +13555,44 @@
       <c r="C26" s="25">
         <v>1</v>
       </c>
-      <c r="D26" s="66" t="s">
+      <c r="D26" s="63" t="s">
         <v>762</v>
       </c>
-      <c r="E26" s="66" t="s">
+      <c r="E26" s="63" t="s">
         <v>363</v>
       </c>
-      <c r="F26" s="66" t="s">
+      <c r="F26" s="63" t="s">
         <v>870</v>
       </c>
-      <c r="G26" s="66" t="s">
+      <c r="G26" s="63" t="s">
         <v>1880</v>
       </c>
-      <c r="H26" s="66" t="s">
+      <c r="H26" s="63" t="s">
         <v>418</v>
       </c>
       <c r="I26" s="28" t="s">
         <v>1645</v>
       </c>
-      <c r="J26" s="67" t="s">
+      <c r="J26" s="64" t="s">
         <v>1776</v>
       </c>
-      <c r="K26" s="70" t="s">
+      <c r="K26" s="67" t="s">
         <v>301</v>
       </c>
-      <c r="L26" s="70" t="s">
+      <c r="L26" s="67" t="s">
         <v>318</v>
       </c>
-      <c r="M26" s="70" t="s">
+      <c r="M26" s="67" t="s">
         <v>315</v>
       </c>
-      <c r="N26" s="70" t="s">
+      <c r="N26" s="67" t="s">
         <v>320</v>
       </c>
       <c r="O26" s="24" t="s">
         <v>151</v>
       </c>
       <c r="P26" s="25">
-        <f>COUNTA(D26:N26)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="Q26" s="30" t="s">
@@ -9428,7 +13602,7 @@
         <v>2180</v>
       </c>
       <c r="S26" s="31"/>
-      <c r="T26" s="105" t="s">
+      <c r="T26" s="98" t="s">
         <v>2199</v>
       </c>
       <c r="U26" s="17"/>
@@ -9471,7 +13645,7 @@
         <v>103</v>
       </c>
       <c r="P27" s="25">
-        <f>COUNTA(D27:N27)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q27" s="30" t="s">
@@ -9523,7 +13697,7 @@
         <v>103</v>
       </c>
       <c r="P28" s="25">
-        <f>COUNTA(D28:N28)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="Q28" s="30" t="s">
@@ -9576,7 +13750,7 @@
         <v>103</v>
       </c>
       <c r="P29" s="25">
-        <f>COUNTA(D29:N29)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="Q29" s="30" t="s">
@@ -9627,7 +13801,7 @@
         <v>103</v>
       </c>
       <c r="P30" s="25">
-        <f>COUNTA(D30:N30)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="Q30" s="30" t="s">
@@ -9637,7 +13811,7 @@
         <v>296</v>
       </c>
       <c r="S30" s="31"/>
-      <c r="T30" s="89" t="s">
+      <c r="T30" s="83" t="s">
         <v>2184</v>
       </c>
       <c r="U30" s="17"/>
@@ -9698,7 +13872,2061 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58C50414-A15B-4944-B114-00412CA5E6E3}">
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="9" max="9" width="32.6640625" customWidth="1"/>
+    <col min="10" max="10" width="72.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="101" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="104" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="102" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="105" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C5" s="105" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D5" s="105" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="192" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="224" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="109" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="224" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8" s="109" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="224" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9" s="109" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="224" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+      <c r="B11" s="102" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C11" s="102">
+        <f>SUM(C6:C10)</f>
+        <v>38</v>
+      </c>
+      <c r="D11" s="109" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="102" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="105" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C14" s="105" t="s">
+        <v>2218</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E14" s="105" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F14" s="105" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D15" s="109" t="s">
+        <v>2390</v>
+      </c>
+      <c r="E15" s="109" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F15" s="109" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="64" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D16" s="109" t="s">
+        <v>2392</v>
+      </c>
+      <c r="E16" s="109" t="s">
+        <v>2227</v>
+      </c>
+      <c r="F16" s="109" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D17" s="109" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E17" s="109" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F17" s="109" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2397</v>
+      </c>
+      <c r="D18" s="109" t="s">
+        <v>2398</v>
+      </c>
+      <c r="E18" s="109" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F18" s="109" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D19" s="109" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E19" s="109"/>
+      <c r="F19" s="109"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="106" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B21" s="106" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C21" s="106" t="s">
+        <v>377</v>
+      </c>
+      <c r="D21" s="106" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E21" s="106" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F21" s="106" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G21" s="106" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H21" s="106" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I21" s="106" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J21" s="106" t="s">
+        <v>2245</v>
+      </c>
+      <c r="K21" s="106" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="107" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B22" s="107"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="107"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="107"/>
+      <c r="H22" s="107"/>
+      <c r="I22" s="107"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+    </row>
+    <row r="23" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A23" s="115">
+        <v>1</v>
+      </c>
+      <c r="B23" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C23" s="116" t="str">
+        <f>FUNDAMENTALS!E21</f>
+        <v>Scapular Pull-ups</v>
+      </c>
+      <c r="D23" s="117">
+        <v>1</v>
+      </c>
+      <c r="E23" s="117">
+        <v>8</v>
+      </c>
+      <c r="F23" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G23" s="117">
+        <v>5</v>
+      </c>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="118" t="s">
+        <v>2402</v>
+      </c>
+      <c r="K23" s="115"/>
+    </row>
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="115">
+        <v>1</v>
+      </c>
+      <c r="B24" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C24" s="116" t="str">
+        <f>FUNDAMENTALS!D26</f>
+        <v>Thoracic Rotations</v>
+      </c>
+      <c r="D24" s="117">
+        <v>1</v>
+      </c>
+      <c r="E24" s="117" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F24" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G24" s="117"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="118" t="s">
+        <v>2403</v>
+      </c>
+      <c r="K24" s="115"/>
+    </row>
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="115">
+        <v>1</v>
+      </c>
+      <c r="B25" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C25" s="116" t="str">
+        <f>FUNDAMENTALS!E16</f>
+        <v>Dip Support Hold</v>
+      </c>
+      <c r="D25" s="117">
+        <v>1</v>
+      </c>
+      <c r="E25" s="117" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F25" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G25" s="117"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="118" t="s">
+        <v>2404</v>
+      </c>
+      <c r="K25" s="115"/>
+    </row>
+    <row r="26" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="115">
+        <v>1</v>
+      </c>
+      <c r="B26" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C26" s="131" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D26" s="117">
+        <v>5</v>
+      </c>
+      <c r="E26" s="117">
+        <v>3</v>
+      </c>
+      <c r="F26" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G26" s="117">
+        <v>5</v>
+      </c>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="118" t="s">
+        <v>2405</v>
+      </c>
+      <c r="K26" s="115"/>
+    </row>
+    <row r="27" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="115">
+        <v>1</v>
+      </c>
+      <c r="B27" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C27" s="116" t="str">
+        <f>FUNDAMENTALS!I16</f>
+        <v>Dip</v>
+      </c>
+      <c r="D27" s="117">
+        <v>3</v>
+      </c>
+      <c r="E27" s="117" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F27" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G27" s="117">
+        <v>11</v>
+      </c>
+      <c r="H27" s="116" t="str">
+        <f>FUNDAMENTALS!H16</f>
+        <v>Banded Dip</v>
+      </c>
+      <c r="I27" s="116" t="str">
+        <f>FUNDAMENTALS!J16</f>
+        <v>Ring Dip</v>
+      </c>
+      <c r="J27" s="118" t="s">
+        <v>2406</v>
+      </c>
+      <c r="K27" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="115">
+        <v>1</v>
+      </c>
+      <c r="B28" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C28" s="116" t="str">
+        <f>FUNDAMENTALS!I5</f>
+        <v>Goblet Squat</v>
+      </c>
+      <c r="D28" s="117">
+        <v>3</v>
+      </c>
+      <c r="E28" s="117">
+        <v>8</v>
+      </c>
+      <c r="F28" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G28" s="117"/>
+      <c r="H28" s="116" t="str">
+        <f>FUNDAMENTALS!H5</f>
+        <v>Slant-Board Squat</v>
+      </c>
+      <c r="I28" s="116" t="str">
+        <f>FUNDAMENTALS!J5</f>
+        <v>Back Squat</v>
+      </c>
+      <c r="J28" s="118" t="s">
+        <v>2407</v>
+      </c>
+      <c r="K28" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A29" s="115">
+        <v>1</v>
+      </c>
+      <c r="B29" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C29" s="116" t="str">
+        <f>FUNDAMENTALS!I15</f>
+        <v>Pike Push-Up</v>
+      </c>
+      <c r="D29" s="117">
+        <v>3</v>
+      </c>
+      <c r="E29" s="117" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F29" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G29" s="117">
+        <v>9</v>
+      </c>
+      <c r="H29" s="116" t="str">
+        <f>FUNDAMENTALS!H15</f>
+        <v>Incline Push-Up</v>
+      </c>
+      <c r="I29" s="116" t="str">
+        <f>FUNDAMENTALS!J15</f>
+        <v>Elevated Pike Push-Up</v>
+      </c>
+      <c r="J29" s="118" t="s">
+        <v>2408</v>
+      </c>
+      <c r="K29" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="115">
+        <v>1</v>
+      </c>
+      <c r="B30" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C30" s="116" t="str">
+        <f>FUNDAMENTALS!I8</f>
+        <v>Bulgarian Split Squat</v>
+      </c>
+      <c r="D30" s="117">
+        <v>3</v>
+      </c>
+      <c r="E30" s="117" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G30" s="117"/>
+      <c r="H30" s="116" t="str">
+        <f>FUNDAMENTALS!H8</f>
+        <v>Racked Reverse Lunge</v>
+      </c>
+      <c r="I30" s="116" t="str">
+        <f>FUNDAMENTALS!J8</f>
+        <v>Barbell Bulgarian Split Squat</v>
+      </c>
+      <c r="J30" s="118" t="s">
+        <v>2264</v>
+      </c>
+      <c r="K30" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A31" s="126">
+        <v>1</v>
+      </c>
+      <c r="B31" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C31" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="D31" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E31" s="128" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F31" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G31" s="128">
+        <v>8</v>
+      </c>
+      <c r="H31" s="127" t="str">
+        <f>FUNDAMENTALS!H24</f>
+        <v>Forearm Plank</v>
+      </c>
+      <c r="I31" s="127" t="str">
+        <f>FUNDAMENTALS!J24</f>
+        <v>Hollow Rock</v>
+      </c>
+      <c r="J31" s="129" t="s">
+        <v>2409</v>
+      </c>
+      <c r="K31" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="126">
+        <v>1</v>
+      </c>
+      <c r="B32" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C32" s="127" t="str">
+        <f>FUNDAMENTALS!I25</f>
+        <v>Side Plank</v>
+      </c>
+      <c r="D32" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E32" s="128" t="s">
+        <v>2339</v>
+      </c>
+      <c r="F32" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G32" s="128"/>
+      <c r="H32" s="127" t="str">
+        <f>FUNDAMENTALS!H25</f>
+        <v>Side Plank (hand on bar)</v>
+      </c>
+      <c r="I32" s="127" t="str">
+        <f>FUNDAMENTALS!J25</f>
+        <v>Side Plank Hip Dip</v>
+      </c>
+      <c r="J32" s="129" t="s">
+        <v>2410</v>
+      </c>
+      <c r="K32" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="126">
+        <v>1</v>
+      </c>
+      <c r="B33" s="126" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C33" s="130" t="s">
+        <v>332</v>
+      </c>
+      <c r="D33" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E33" s="128">
+        <v>8</v>
+      </c>
+      <c r="F33" s="128" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G33" s="128"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="129" t="s">
+        <v>2411</v>
+      </c>
+      <c r="K33" s="126" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="108"/>
+      <c r="B34" s="108" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108">
+        <f>SUM(G23:G33)</f>
+        <v>38</v>
+      </c>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="107" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B36" s="107"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="107"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
+      <c r="K36" s="107"/>
+    </row>
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="115">
+        <v>2</v>
+      </c>
+      <c r="B37" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C37" s="116" t="str">
+        <f>FUNDAMENTALS!E21</f>
+        <v>Scapular Pull-ups</v>
+      </c>
+      <c r="D37" s="117">
+        <v>1</v>
+      </c>
+      <c r="E37" s="117">
+        <v>8</v>
+      </c>
+      <c r="F37" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G37" s="117">
+        <v>5</v>
+      </c>
+      <c r="H37" s="116"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="118" t="s">
+        <v>2413</v>
+      </c>
+      <c r="K37" s="115"/>
+    </row>
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="115">
+        <v>2</v>
+      </c>
+      <c r="B38" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C38" s="116" t="str">
+        <f>FUNDAMENTALS!E26</f>
+        <v>90/90 Hip Switches</v>
+      </c>
+      <c r="D38" s="117">
+        <v>1</v>
+      </c>
+      <c r="E38" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F38" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G38" s="117"/>
+      <c r="H38" s="116"/>
+      <c r="I38" s="116"/>
+      <c r="J38" s="118" t="s">
+        <v>2414</v>
+      </c>
+      <c r="K38" s="115"/>
+    </row>
+    <row r="39" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="115">
+        <v>2</v>
+      </c>
+      <c r="B39" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C39" s="116" t="str">
+        <f>FUNDAMENTALS!H19</f>
+        <v>Active Hang</v>
+      </c>
+      <c r="D39" s="117">
+        <v>1</v>
+      </c>
+      <c r="E39" s="117" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F39" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G39" s="117"/>
+      <c r="H39" s="116"/>
+      <c r="I39" s="116"/>
+      <c r="J39" s="118" t="s">
+        <v>2415</v>
+      </c>
+      <c r="K39" s="115"/>
+    </row>
+    <row r="40" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A40" s="115">
+        <v>2</v>
+      </c>
+      <c r="B40" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C40" s="116" t="str">
+        <f>FUNDAMENTALS!J6</f>
+        <v>Kettlebell Swing</v>
+      </c>
+      <c r="D40" s="117">
+        <v>5</v>
+      </c>
+      <c r="E40" s="117">
+        <v>8</v>
+      </c>
+      <c r="F40" s="117" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G40" s="117">
+        <v>5</v>
+      </c>
+      <c r="H40" s="116"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="118" t="s">
+        <v>2416</v>
+      </c>
+      <c r="K40" s="115"/>
+    </row>
+    <row r="41" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A41" s="115">
+        <v>2</v>
+      </c>
+      <c r="B41" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C41" s="116" t="str">
+        <f>FUNDAMENTALS!I21</f>
+        <v>Pull-Up</v>
+      </c>
+      <c r="D41" s="117">
+        <v>3</v>
+      </c>
+      <c r="E41" s="117" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F41" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G41" s="117">
+        <v>11</v>
+      </c>
+      <c r="H41" s="116" t="str">
+        <f>FUNDAMENTALS!H21</f>
+        <v>Negative Pull-Up</v>
+      </c>
+      <c r="I41" s="116" t="str">
+        <f>FUNDAMENTALS!J21</f>
+        <v>Wide-Grip Pull-Up</v>
+      </c>
+      <c r="J41" s="118" t="s">
+        <v>2417</v>
+      </c>
+      <c r="K41" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="115">
+        <v>2</v>
+      </c>
+      <c r="B42" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C42" s="116" t="str">
+        <f>FUNDAMENTALS!I6</f>
+        <v>Romanian Deadlift</v>
+      </c>
+      <c r="D42" s="117">
+        <v>3</v>
+      </c>
+      <c r="E42" s="117">
+        <v>8</v>
+      </c>
+      <c r="F42" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G42" s="117"/>
+      <c r="H42" s="116" t="str">
+        <f>FUNDAMENTALS!H6</f>
+        <v>Dumbbell Romanian Deadlift</v>
+      </c>
+      <c r="I42" s="116" t="str">
+        <f>FUNDAMENTALS!K6</f>
+        <v>Single-Leg RDL</v>
+      </c>
+      <c r="J42" s="118" t="s">
+        <v>2276</v>
+      </c>
+      <c r="K42" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="115">
+        <v>2</v>
+      </c>
+      <c r="B43" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C43" s="116" t="str">
+        <f>FUNDAMENTALS!I20</f>
+        <v>Wide Inverted Row</v>
+      </c>
+      <c r="D43" s="117">
+        <v>3</v>
+      </c>
+      <c r="E43" s="117" t="s">
+        <v>2418</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G43" s="117">
+        <v>9</v>
+      </c>
+      <c r="H43" s="116" t="str">
+        <f>FUNDAMENTALS!H20</f>
+        <v>Australian Pull-Up</v>
+      </c>
+      <c r="I43" s="116" t="str">
+        <f>FUNDAMENTALS!J20</f>
+        <v>Feet-Elevated Ring Row</v>
+      </c>
+      <c r="J43" s="118" t="s">
+        <v>2419</v>
+      </c>
+      <c r="K43" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A44" s="115">
+        <v>2</v>
+      </c>
+      <c r="B44" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C44" s="116" t="str">
+        <f>FUNDAMENTALS!I7</f>
+        <v>Hip Thrust</v>
+      </c>
+      <c r="D44" s="117">
+        <v>3</v>
+      </c>
+      <c r="E44" s="117">
+        <v>10</v>
+      </c>
+      <c r="F44" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G44" s="117"/>
+      <c r="H44" s="116" t="str">
+        <f>FUNDAMENTALS!H7</f>
+        <v>Banded Glute Bridge</v>
+      </c>
+      <c r="I44" s="116" t="str">
+        <f>FUNDAMENTALS!J7</f>
+        <v>Barbell Hip Thrust</v>
+      </c>
+      <c r="J44" s="118" t="s">
+        <v>2420</v>
+      </c>
+      <c r="K44" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A45" s="126">
+        <v>2</v>
+      </c>
+      <c r="B45" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C45" s="127" t="str">
+        <f>FUNDAMENTALS!I28</f>
+        <v>Hanging Leg Raise</v>
+      </c>
+      <c r="D45" s="128" t="s">
+        <v>2346</v>
+      </c>
+      <c r="E45" s="128">
+        <v>8</v>
+      </c>
+      <c r="F45" s="128" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G45" s="128">
+        <v>8</v>
+      </c>
+      <c r="H45" s="127" t="str">
+        <f>FUNDAMENTALS!H28</f>
+        <v>Hanging Knee Raise</v>
+      </c>
+      <c r="I45" s="127" t="str">
+        <f>FUNDAMENTALS!J28</f>
+        <v>Toes-to-Bar</v>
+      </c>
+      <c r="J45" s="129" t="s">
+        <v>2421</v>
+      </c>
+      <c r="K45" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A46" s="126">
+        <v>2</v>
+      </c>
+      <c r="B46" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C46" s="127" t="str">
+        <f>FUNDAMENTALS!I27</f>
+        <v>Pallof Press</v>
+      </c>
+      <c r="D46" s="128" t="s">
+        <v>2349</v>
+      </c>
+      <c r="E46" s="128" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F46" s="128" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G46" s="128"/>
+      <c r="H46" s="127" t="str">
+        <f>FUNDAMENTALS!H27</f>
+        <v>Bird Dog</v>
+      </c>
+      <c r="I46" s="127" t="str">
+        <f>FUNDAMENTALS!J27</f>
+        <v>Half-Kneeling Cable Chop</v>
+      </c>
+      <c r="J46" s="129" t="s">
+        <v>2422</v>
+      </c>
+      <c r="K46" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A47" s="126">
+        <v>2</v>
+      </c>
+      <c r="B47" s="126" t="s">
+        <v>2345</v>
+      </c>
+      <c r="C47" s="127" t="str">
+        <f>FUNDAMENTALS!E19</f>
+        <v>Farmer's Carry (no straps)</v>
+      </c>
+      <c r="D47" s="128" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E47" s="128" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F47" s="128" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G47" s="128"/>
+      <c r="H47" s="130" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I47" s="130" t="str">
+        <f>FUNDAMENTALS!F19</f>
+        <v>Suitcase Carry</v>
+      </c>
+      <c r="J47" s="129" t="s">
+        <v>2423</v>
+      </c>
+      <c r="K47" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="108"/>
+      <c r="B48" s="108" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="108">
+        <f>SUM(G37:G47)</f>
+        <v>38</v>
+      </c>
+      <c r="H48" s="108"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="108"/>
+      <c r="K48" s="108"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="107" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B50" s="107"/>
+      <c r="C50" s="107"/>
+      <c r="D50" s="107"/>
+      <c r="E50" s="107"/>
+      <c r="F50" s="107"/>
+      <c r="G50" s="107"/>
+      <c r="H50" s="107"/>
+      <c r="I50" s="107"/>
+      <c r="J50" s="107"/>
+      <c r="K50" s="107"/>
+    </row>
+    <row r="51" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A51" s="115">
+        <v>3</v>
+      </c>
+      <c r="B51" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C51" s="116" t="str">
+        <f>FUNDAMENTALS!G11</f>
+        <v>Prying Goblet Squat</v>
+      </c>
+      <c r="D51" s="117">
+        <v>1</v>
+      </c>
+      <c r="E51" s="117" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F51" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G51" s="117">
+        <v>5</v>
+      </c>
+      <c r="H51" s="116"/>
+      <c r="I51" s="116"/>
+      <c r="J51" s="118" t="s">
+        <v>2425</v>
+      </c>
+      <c r="K51" s="115"/>
+    </row>
+    <row r="52" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="115">
+        <v>3</v>
+      </c>
+      <c r="B52" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C52" s="116" t="str">
+        <f>FUNDAMENTALS!F11</f>
+        <v>Banded Lateral Walks</v>
+      </c>
+      <c r="D52" s="117">
+        <v>1</v>
+      </c>
+      <c r="E52" s="117" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F52" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G52" s="117"/>
+      <c r="H52" s="116"/>
+      <c r="I52" s="116"/>
+      <c r="J52" s="118" t="s">
+        <v>2426</v>
+      </c>
+      <c r="K52" s="115"/>
+    </row>
+    <row r="53" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A53" s="115">
+        <v>3</v>
+      </c>
+      <c r="B53" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C53" s="116" t="str">
+        <f>FUNDAMENTALS!D26</f>
+        <v>Thoracic Rotations</v>
+      </c>
+      <c r="D53" s="117">
+        <v>1</v>
+      </c>
+      <c r="E53" s="117" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F53" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G53" s="117"/>
+      <c r="H53" s="116"/>
+      <c r="I53" s="116"/>
+      <c r="J53" s="118" t="s">
+        <v>2427</v>
+      </c>
+      <c r="K53" s="115"/>
+    </row>
+    <row r="54" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A54" s="115">
+        <v>3</v>
+      </c>
+      <c r="B54" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C54" s="116" t="str">
+        <f>FUNDAMENTALS!N26</f>
+        <v>Rotational Medicine Ball Throw</v>
+      </c>
+      <c r="D54" s="117">
+        <v>3</v>
+      </c>
+      <c r="E54" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F54" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G54" s="117">
+        <v>5</v>
+      </c>
+      <c r="H54" s="116"/>
+      <c r="I54" s="116"/>
+      <c r="J54" s="118" t="s">
+        <v>2428</v>
+      </c>
+      <c r="K54" s="115"/>
+    </row>
+    <row r="55" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A55" s="115">
+        <v>3</v>
+      </c>
+      <c r="B55" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C55" s="116" t="str">
+        <f>FUNDAMENTALS!I14</f>
+        <v>Push-ups</v>
+      </c>
+      <c r="D55" s="117">
+        <v>4</v>
+      </c>
+      <c r="E55" s="117" t="s">
+        <v>2429</v>
+      </c>
+      <c r="F55" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G55" s="117">
+        <v>11</v>
+      </c>
+      <c r="H55" s="116" t="str">
+        <f>FUNDAMENTALS!H14</f>
+        <v>Knee Push-Up</v>
+      </c>
+      <c r="I55" s="116" t="str">
+        <f>FUNDAMENTALS!J14</f>
+        <v>Decline Push-Up</v>
+      </c>
+      <c r="J55" s="118" t="s">
+        <v>2430</v>
+      </c>
+      <c r="K55" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A56" s="115">
+        <v>3</v>
+      </c>
+      <c r="B56" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C56" s="116" t="str">
+        <f>FUNDAMENTALS!I11</f>
+        <v>Cossack Squat</v>
+      </c>
+      <c r="D56" s="117">
+        <v>3</v>
+      </c>
+      <c r="E56" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F56" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G56" s="117"/>
+      <c r="H56" s="116" t="str">
+        <f>FUNDAMENTALS!H11</f>
+        <v>Kettlebell Cossack Squat</v>
+      </c>
+      <c r="I56" s="116" t="str">
+        <f>FUNDAMENTALS!J11</f>
+        <v>Goblet Lateral Lunge</v>
+      </c>
+      <c r="J56" s="118" t="s">
+        <v>2431</v>
+      </c>
+      <c r="K56" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="115">
+        <v>3</v>
+      </c>
+      <c r="B57" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C57" s="116" t="str">
+        <f>FUNDAMENTALS!I17</f>
+        <v>Wall Handstand</v>
+      </c>
+      <c r="D57" s="117">
+        <v>3</v>
+      </c>
+      <c r="E57" s="117" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F57" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G57" s="117">
+        <v>9</v>
+      </c>
+      <c r="H57" s="116" t="str">
+        <f>FUNDAMENTALS!H17</f>
+        <v>Wall Walk</v>
+      </c>
+      <c r="I57" s="116" t="str">
+        <f>FUNDAMENTALS!J17</f>
+        <v>Back-to-Wall Handstand Hold</v>
+      </c>
+      <c r="J57" s="118" t="s">
+        <v>2303</v>
+      </c>
+      <c r="K57" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A58" s="115">
+        <v>3</v>
+      </c>
+      <c r="B58" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C58" s="116" t="str">
+        <f>FUNDAMENTALS!I12</f>
+        <v>Reverse Nordic Curl</v>
+      </c>
+      <c r="D58" s="117">
+        <v>3</v>
+      </c>
+      <c r="E58" s="117">
+        <v>8</v>
+      </c>
+      <c r="F58" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G58" s="117"/>
+      <c r="H58" s="116" t="str">
+        <f>FUNDAMENTALS!H12</f>
+        <v>Assisted Reverse Nordic Curl</v>
+      </c>
+      <c r="I58" s="116" t="str">
+        <f>FUNDAMENTALS!J12</f>
+        <v>Sissy Squat</v>
+      </c>
+      <c r="J58" s="118" t="s">
+        <v>2432</v>
+      </c>
+      <c r="K58" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A59" s="126">
+        <v>3</v>
+      </c>
+      <c r="B59" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C59" s="127" t="str">
+        <f>FUNDAMENTALS!J24</f>
+        <v>Hollow Rock</v>
+      </c>
+      <c r="D59" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E59" s="128">
+        <v>12</v>
+      </c>
+      <c r="F59" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G59" s="128">
+        <v>8</v>
+      </c>
+      <c r="H59" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="I59" s="127" t="str">
+        <f>FUNDAMENTALS!K24</f>
+        <v>Squeeze-Loaded Hollow Hold</v>
+      </c>
+      <c r="J59" s="129" t="s">
+        <v>2433</v>
+      </c>
+      <c r="K59" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A60" s="126">
+        <v>3</v>
+      </c>
+      <c r="B60" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C60" s="127" t="str">
+        <f>FUNDAMENTALS!I26</f>
+        <v>Weighted Russian Twist</v>
+      </c>
+      <c r="D60" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E60" s="128">
+        <v>12</v>
+      </c>
+      <c r="F60" s="128" t="s">
+        <v>2337</v>
+      </c>
+      <c r="G60" s="128"/>
+      <c r="H60" s="127" t="str">
+        <f>FUNDAMENTALS!H26</f>
+        <v>Half-Kneeling Rotation</v>
+      </c>
+      <c r="I60" s="127" t="str">
+        <f>FUNDAMENTALS!J26</f>
+        <v>Kettlebell Figure-8</v>
+      </c>
+      <c r="J60" s="129" t="s">
+        <v>2434</v>
+      </c>
+      <c r="K60" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A61" s="126">
+        <v>3</v>
+      </c>
+      <c r="B61" s="126" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C61" s="130" t="str">
+        <f>FUNDAMENTALS!J6</f>
+        <v>Kettlebell Swing</v>
+      </c>
+      <c r="D61" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E61" s="128">
+        <v>15</v>
+      </c>
+      <c r="F61" s="128" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G61" s="128"/>
+      <c r="H61" s="130" t="s">
+        <v>2359</v>
+      </c>
+      <c r="I61" s="130" t="s">
+        <v>2360</v>
+      </c>
+      <c r="J61" s="129" t="s">
+        <v>2361</v>
+      </c>
+      <c r="K61" s="126" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="108"/>
+      <c r="B62" s="108" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108">
+        <f>SUM(G51:G61)</f>
+        <v>38</v>
+      </c>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="108"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="107" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B64" s="107"/>
+      <c r="C64" s="107"/>
+      <c r="D64" s="107"/>
+      <c r="E64" s="107"/>
+      <c r="F64" s="107"/>
+      <c r="G64" s="107"/>
+      <c r="H64" s="107"/>
+      <c r="I64" s="107"/>
+      <c r="J64" s="107"/>
+      <c r="K64" s="107"/>
+    </row>
+    <row r="65" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="115">
+        <v>4</v>
+      </c>
+      <c r="B65" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C65" s="131" t="s">
+        <v>360</v>
+      </c>
+      <c r="D65" s="117">
+        <v>1</v>
+      </c>
+      <c r="E65" s="117" t="s">
+        <v>2248</v>
+      </c>
+      <c r="F65" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G65" s="117">
+        <v>5</v>
+      </c>
+      <c r="H65" s="116"/>
+      <c r="I65" s="116"/>
+      <c r="J65" s="118" t="s">
+        <v>2295</v>
+      </c>
+      <c r="K65" s="115"/>
+    </row>
+    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="115">
+        <v>4</v>
+      </c>
+      <c r="B66" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C66" s="116" t="str">
+        <f>FUNDAMENTALS!E26</f>
+        <v>90/90 Hip Switches</v>
+      </c>
+      <c r="D66" s="117">
+        <v>1</v>
+      </c>
+      <c r="E66" s="117" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F66" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G66" s="117"/>
+      <c r="H66" s="116"/>
+      <c r="I66" s="116"/>
+      <c r="J66" s="118" t="s">
+        <v>2436</v>
+      </c>
+      <c r="K66" s="115"/>
+    </row>
+    <row r="67" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A67" s="115">
+        <v>4</v>
+      </c>
+      <c r="B67" s="115" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C67" s="116" t="str">
+        <f>FUNDAMENTALS!E22</f>
+        <v>German Hang</v>
+      </c>
+      <c r="D67" s="117">
+        <v>1</v>
+      </c>
+      <c r="E67" s="117" t="s">
+        <v>2437</v>
+      </c>
+      <c r="F67" s="117" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G67" s="117"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="116"/>
+      <c r="J67" s="118" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K67" s="115"/>
+    </row>
+    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="115">
+        <v>4</v>
+      </c>
+      <c r="B68" s="115" t="s">
+        <v>2208</v>
+      </c>
+      <c r="C68" s="131" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D68" s="117">
+        <v>3</v>
+      </c>
+      <c r="E68" s="117">
+        <v>5</v>
+      </c>
+      <c r="F68" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G68" s="117">
+        <v>5</v>
+      </c>
+      <c r="H68" s="116"/>
+      <c r="I68" s="116"/>
+      <c r="J68" s="118" t="s">
+        <v>2439</v>
+      </c>
+      <c r="K68" s="115"/>
+    </row>
+    <row r="69" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A69" s="115">
+        <v>4</v>
+      </c>
+      <c r="B69" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C69" s="116" t="str">
+        <f>FUNDAMENTALS!I22</f>
+        <v>Band-Assisted Front Lever</v>
+      </c>
+      <c r="D69" s="117">
+        <v>4</v>
+      </c>
+      <c r="E69" s="117" t="s">
+        <v>2440</v>
+      </c>
+      <c r="F69" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G69" s="117">
+        <v>11</v>
+      </c>
+      <c r="H69" s="116" t="str">
+        <f>FUNDAMENTALS!H22</f>
+        <v>Tuck Front Lever Raise</v>
+      </c>
+      <c r="I69" s="116" t="str">
+        <f>FUNDAMENTALS!J22</f>
+        <v>Adv-Tuck FL Raise</v>
+      </c>
+      <c r="J69" s="118" t="s">
+        <v>2441</v>
+      </c>
+      <c r="K69" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A70" s="115">
+        <v>4</v>
+      </c>
+      <c r="B70" s="115" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C70" s="116" t="str">
+        <f>FUNDAMENTALS!I10</f>
+        <v>Nordic Curl</v>
+      </c>
+      <c r="D70" s="117">
+        <v>3</v>
+      </c>
+      <c r="E70" s="117">
+        <v>5</v>
+      </c>
+      <c r="F70" s="117" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G70" s="117"/>
+      <c r="H70" s="116" t="str">
+        <f>FUNDAMENTALS!H10</f>
+        <v>Sliding Hamstring Curl</v>
+      </c>
+      <c r="I70" s="131" t="s">
+        <v>2300</v>
+      </c>
+      <c r="J70" s="118" t="s">
+        <v>2442</v>
+      </c>
+      <c r="K70" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A71" s="115">
+        <v>4</v>
+      </c>
+      <c r="B71" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C71" s="116" t="str">
+        <f>FUNDAMENTALS!I19</f>
+        <v>Dead Hang</v>
+      </c>
+      <c r="D71" s="117">
+        <v>3</v>
+      </c>
+      <c r="E71" s="117" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F71" s="117" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G71" s="117">
+        <v>9</v>
+      </c>
+      <c r="H71" s="116" t="str">
+        <f>FUNDAMENTALS!H19</f>
+        <v>Active Hang</v>
+      </c>
+      <c r="I71" s="116" t="str">
+        <f>FUNDAMENTALS!J19</f>
+        <v>Towel Hang</v>
+      </c>
+      <c r="J71" s="118" t="s">
+        <v>2443</v>
+      </c>
+      <c r="K71" s="115" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A72" s="115">
+        <v>4</v>
+      </c>
+      <c r="B72" s="115" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C72" s="116" t="str">
+        <f>FUNDAMENTALS!I9</f>
+        <v>Wall Sit</v>
+      </c>
+      <c r="D72" s="117">
+        <v>3</v>
+      </c>
+      <c r="E72" s="117" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F72" s="117" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G72" s="117"/>
+      <c r="H72" s="131" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I72" s="116" t="str">
+        <f>FUNDAMENTALS!J9</f>
+        <v>Horse Stance</v>
+      </c>
+      <c r="J72" s="118" t="s">
+        <v>2306</v>
+      </c>
+      <c r="K72" s="115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A73" s="126">
+        <v>4</v>
+      </c>
+      <c r="B73" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C73" s="127" t="str">
+        <f>FUNDAMENTALS!F29</f>
+        <v>Dragon Flag (Tuck)</v>
+      </c>
+      <c r="D73" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E73" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F73" s="128" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G73" s="128">
+        <v>8</v>
+      </c>
+      <c r="H73" s="127" t="str">
+        <f>FUNDAMENTALS!E29</f>
+        <v>Dragon Flag Candlestick</v>
+      </c>
+      <c r="I73" s="127" t="str">
+        <f>FUNDAMENTALS!G29</f>
+        <v>Tuck Dragon Flag Hold</v>
+      </c>
+      <c r="J73" s="129" t="s">
+        <v>2366</v>
+      </c>
+      <c r="K73" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A74" s="126">
+        <v>4</v>
+      </c>
+      <c r="B74" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C74" s="127" t="str">
+        <f>FUNDAMENTALS!J25</f>
+        <v>Side Plank Hip Dip</v>
+      </c>
+      <c r="D74" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E74" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F74" s="128" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G74" s="128"/>
+      <c r="H74" s="127" t="str">
+        <f>FUNDAMENTALS!I25</f>
+        <v>Side Plank</v>
+      </c>
+      <c r="I74" s="127" t="str">
+        <f>FUNDAMENTALS!K25</f>
+        <v>Star Side Plank</v>
+      </c>
+      <c r="J74" s="129" t="s">
+        <v>2444</v>
+      </c>
+      <c r="K74" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="A75" s="126">
+        <v>4</v>
+      </c>
+      <c r="B75" s="126" t="s">
+        <v>2362</v>
+      </c>
+      <c r="C75" s="127" t="str">
+        <f>FUNDAMENTALS!H24</f>
+        <v>Forearm Plank</v>
+      </c>
+      <c r="D75" s="128" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E75" s="128" t="s">
+        <v>2363</v>
+      </c>
+      <c r="F75" s="128" t="s">
+        <v>2367</v>
+      </c>
+      <c r="G75" s="128"/>
+      <c r="H75" s="130" t="s">
+        <v>2368</v>
+      </c>
+      <c r="I75" s="127" t="str">
+        <f>FUNDAMENTALS!I24</f>
+        <v>Hollow Hold</v>
+      </c>
+      <c r="J75" s="129" t="s">
+        <v>2369</v>
+      </c>
+      <c r="K75" s="126" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A76" s="108"/>
+      <c r="B76" s="108" t="s">
+        <v>2308</v>
+      </c>
+      <c r="C76" s="108"/>
+      <c r="D76" s="108"/>
+      <c r="E76" s="108"/>
+      <c r="F76" s="108"/>
+      <c r="G76" s="108">
+        <f>SUM(G65:G75)</f>
+        <v>38</v>
+      </c>
+      <c r="H76" s="108"/>
+      <c r="I76" s="108"/>
+      <c r="J76" s="108"/>
+      <c r="K76" s="108"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A78" s="102" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B79" s="124" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C79" s="124" t="s">
+        <v>2312</v>
+      </c>
+      <c r="D79" s="124" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B80" s="115" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="115">
+        <f>COUNTIF($K$23:$K$75,$B80)</f>
+        <v>8</v>
+      </c>
+      <c r="D80" s="132">
+        <f>C80/($C$80+$C$81)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B81" s="115" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C81" s="115">
+        <f>COUNTIF($K$23:$K$75,$B81)</f>
+        <v>8</v>
+      </c>
+      <c r="D81" s="132">
+        <f>C81/($C$80+$C$81)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="B82" s="115" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C82" s="115">
+        <f>COUNTIF($K$23:$K$75,"Core")</f>
+        <v>10</v>
+      </c>
+      <c r="D82" s="118" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+      <c r="B83" s="115" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C83" s="115">
+        <f>COUNTIF($K$23:$K$75,"Cond")</f>
+        <v>2</v>
+      </c>
+      <c r="D83" s="118" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="B84" s="123" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C84" s="123">
+        <f>G34+G48+G62+G76</f>
+        <v>152</v>
+      </c>
+      <c r="D84" s="118" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="240" x14ac:dyDescent="0.2">
+      <c r="B85" s="115" t="s">
+        <v>2447</v>
+      </c>
+      <c r="C85" s="115"/>
+      <c r="D85" s="118" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="240" x14ac:dyDescent="0.2">
+      <c r="B86" s="115" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C86" s="115"/>
+      <c r="D86" s="118" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="192" x14ac:dyDescent="0.2">
+      <c r="B87" s="115" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C87" s="115"/>
+      <c r="D87" s="118" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="144" x14ac:dyDescent="0.2">
+      <c r="B88" s="115" t="s">
+        <v>2374</v>
+      </c>
+      <c r="C88" s="115"/>
+      <c r="D88" s="118" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="102" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B89" s="115"/>
+      <c r="C89" s="115"/>
+      <c r="D89" s="115"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B90" s="124" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C90" s="124" t="s">
+        <v>2326</v>
+      </c>
+      <c r="D90" s="115"/>
+    </row>
+    <row r="91" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B91" s="115" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C91" s="118" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D91" s="115"/>
+    </row>
+    <row r="92" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B92" s="115" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C92" s="118" t="s">
+        <v>2344</v>
+      </c>
+      <c r="D92" s="115"/>
+    </row>
+    <row r="93" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B93" s="115" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C93" s="118" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D93" s="115"/>
+    </row>
+    <row r="94" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B94" s="115" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C94" s="118" t="s">
+        <v>2333</v>
+      </c>
+      <c r="D94" s="115"/>
+    </row>
+    <row r="95" spans="1:4" ht="64" x14ac:dyDescent="0.2">
+      <c r="B95" s="115" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C95" s="118" t="s">
+        <v>2335</v>
+      </c>
+      <c r="D95" s="115"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9715,21 +15943,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="99" t="s">
         <v>375</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
     </row>
     <row r="3" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
@@ -12656,7 +18884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AV467"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -65805,7 +72033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H483"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -77010,7 +83238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -77026,16 +83254,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="99" t="s">
         <v>2094</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -79717,7 +85945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -79730,16 +85958,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="99" t="s">
         <v>2124</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -80272,1075 +86500,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4012A2FE-2E88-2345-BAC5-0FBF199696AF}">
-  <dimension ref="A1:V76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="7" customWidth="1"/>
-    <col min="17" max="17" width="26" customWidth="1"/>
-    <col min="18" max="18" width="46" customWidth="1"/>
-    <col min="19" max="19" width="30" customWidth="1"/>
-    <col min="20" max="20" width="46" customWidth="1"/>
-    <col min="21" max="22" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
-        <v>2191</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-    </row>
-    <row r="3" spans="1:22" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="P3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="R3" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="T3" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="U3" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="V3" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="62" t="s">
-        <v>2162</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="62"/>
-    </row>
-    <row r="5" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="25">
-        <v>1</v>
-      </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="25">
-        <f>COUNTA(D5:N5)-COUNTIF(D5:N5,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T5" s="35" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="25">
-        <v>1</v>
-      </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="69" t="s">
-        <v>2000</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="69" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="J6" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="K6" s="70" t="s">
-        <v>117</v>
-      </c>
-      <c r="L6" s="70" t="s">
-        <v>420</v>
-      </c>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="25">
-        <f>COUNTA(D6:N6)-COUNTIF(D6:N6,"no honest gym equivalent")</f>
-        <v>7</v>
-      </c>
-      <c r="T6" s="35" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="25">
-        <v>1</v>
-      </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="25">
-        <f>COUNTA(D7:N7)-COUNTIF(D7:N7,"no honest gym equivalent")</f>
-        <v>3</v>
-      </c>
-      <c r="T7" s="35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="25">
-        <v>1</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="25">
-        <f>COUNTA(D8:N8)-COUNTIF(D8:N8,"no honest gym equivalent")</f>
-        <v>3</v>
-      </c>
-      <c r="T8" s="35" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="64" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>2186</v>
-      </c>
-      <c r="C9" s="93">
-        <v>1</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="68" t="s">
-        <v>364</v>
-      </c>
-      <c r="I9" s="92" t="s">
-        <v>99</v>
-      </c>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="94">
-        <f>COUNTA(D9:N9)-COUNTIF(D9:N9,"no honest gym equivalent")</f>
-        <v>2</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="25">
-        <v>2</v>
-      </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="69" t="s">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="69" t="s">
-        <v>145</v>
-      </c>
-      <c r="H10" s="69" t="s">
-        <v>120</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="J10" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="65"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="25">
-        <f>COUNTA(D10:N10)-COUNTIF(D10:N10,"no honest gym equivalent")</f>
-        <v>5</v>
-      </c>
-      <c r="T10" s="35" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C11" s="25">
-        <v>2</v>
-      </c>
-      <c r="D11" s="71"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="73" t="s">
-        <v>1616</v>
-      </c>
-      <c r="H11" s="73" t="s">
-        <v>1846</v>
-      </c>
-      <c r="I11" s="75" t="s">
-        <v>1915</v>
-      </c>
-      <c r="J11" s="74" t="s">
-        <v>319</v>
-      </c>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="32"/>
-      <c r="P11" s="32">
-        <f>COUNTA(D11:N11)-COUNTIF(D11:N11,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T11" s="35" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="82" t="s">
-        <v>2192</v>
-      </c>
-      <c r="B12" s="77" t="s">
-        <v>2181</v>
-      </c>
-      <c r="C12" s="86">
-        <v>2</v>
-      </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="84" t="s">
-        <v>2051</v>
-      </c>
-      <c r="G12" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="83" t="s">
-        <v>2060</v>
-      </c>
-      <c r="I12" s="85" t="s">
-        <v>2057</v>
-      </c>
-      <c r="J12" s="74" t="s">
-        <v>2055</v>
-      </c>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="80"/>
-      <c r="P12" s="90">
-        <f>COUNTA(D12:N12)-COUNTIF(D12:N12,"no honest gym equivalent")</f>
-        <v>5</v>
-      </c>
-      <c r="T12" s="35" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="63" t="s">
-        <v>2163</v>
-      </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="62"/>
-      <c r="L13" s="62"/>
-      <c r="M13" s="62"/>
-      <c r="N13" s="62"/>
-      <c r="O13" s="62"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="62"/>
-      <c r="T13" s="62"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
-    </row>
-    <row r="14" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C14" s="25">
-        <v>1</v>
-      </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="33" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="25">
-        <f>COUNTA(D14:N14)-COUNTIF(D14:N14,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T14" s="35" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="64" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="25">
-        <v>1</v>
-      </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="25">
-        <f>COUNTA(D15:N15)-COUNTIF(D15:N15,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T15" s="35" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="64" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="25">
-        <v>2</v>
-      </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="25">
-        <f>COUNTA(D16:N16)-COUNTIF(D16:N16,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T16" s="35" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="64" t="s">
-        <v>204</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C17" s="25">
-        <v>2</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32">
-        <f>COUNTA(D17:N17)-COUNTIF(D17:N17,"no honest gym equivalent")</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="35" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63" t="s">
-        <v>2164</v>
-      </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
-      <c r="J18" s="62"/>
-      <c r="K18" s="62"/>
-      <c r="L18" s="62"/>
-      <c r="M18" s="62"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="62"/>
-      <c r="Q18" s="62"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="62"/>
-      <c r="T18" s="62"/>
-      <c r="U18" s="62"/>
-      <c r="V18" s="62"/>
-    </row>
-    <row r="19" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="64" t="s">
-        <v>232</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="C19" s="25">
-        <v>1</v>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="H19" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="J19" s="70" t="s">
-        <v>1670</v>
-      </c>
-      <c r="K19" s="70" t="s">
-        <v>1684</v>
-      </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="25">
-        <f>COUNTA(D19:N19)-COUNTIF(D19:N19,"no honest gym equivalent")</f>
-        <v>5</v>
-      </c>
-      <c r="T19" s="35" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="25">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="J20" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="K20" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="L20" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="25">
-        <f>COUNTA(D20:N20)-COUNTIF(D20:N20,"no honest gym equivalent")</f>
-        <v>5</v>
-      </c>
-      <c r="T20" s="35" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="64" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>231</v>
-      </c>
-      <c r="C21" s="25">
-        <v>2</v>
-      </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="32"/>
-      <c r="P21" s="25">
-        <f>COUNTA(D21:N21)-COUNTIF(D21:N21,"no honest gym equivalent")</f>
-        <v>3</v>
-      </c>
-      <c r="T21" s="35" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="C22" s="25">
-        <v>3</v>
-      </c>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="69" t="s">
-        <v>553</v>
-      </c>
-      <c r="H22" s="69" t="s">
-        <v>264</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="J22" s="70" t="s">
-        <v>1939</v>
-      </c>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="25">
-        <f>COUNTA(D22:N22)-COUNTIF(D22:N22,"no honest gym equivalent")</f>
-        <v>4</v>
-      </c>
-      <c r="T22" s="35" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="63" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62"/>
-    </row>
-    <row r="24" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="64" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="C24" s="25">
-        <v>1</v>
-      </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="25">
-        <f>COUNTA(D24:N24)-COUNTIF(D24:N24,"no honest gym equivalent")</f>
-        <v>2</v>
-      </c>
-      <c r="T24" s="35" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="64" t="s">
-        <v>305</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="25">
-        <v>1</v>
-      </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="32"/>
-      <c r="P25" s="25">
-        <f>COUNTA(D25:N25)-COUNTIF(D25:N25,"no honest gym equivalent")</f>
-        <v>2</v>
-      </c>
-      <c r="T25" s="35" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="64" t="s">
-        <v>1645</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="C26" s="25">
-        <v>1</v>
-      </c>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="69" t="s">
-        <v>1645</v>
-      </c>
-      <c r="H26" s="69" t="s">
-        <v>317</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="J26" s="70" t="s">
-        <v>318</v>
-      </c>
-      <c r="K26" s="70" t="s">
-        <v>320</v>
-      </c>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="32"/>
-      <c r="P26" s="25">
-        <f>COUNTA(D26:N26)-COUNTIF(D26:N26,"no honest gym equivalent")</f>
-        <v>5</v>
-      </c>
-      <c r="T26" s="35" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="64" t="s">
-        <v>312</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="C27" s="25">
-        <v>1</v>
-      </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="25">
-        <f>COUNTA(D27:N27)-COUNTIF(D27:N27,"no honest gym equivalent")</f>
-        <v>2</v>
-      </c>
-      <c r="T27" s="35" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="64" t="s">
-        <v>298</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="C28" s="25">
-        <v>2</v>
-      </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>278</v>
-      </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="25">
-        <f>COUNTA(D28:N28)-COUNTIF(D28:N28,"no honest gym equivalent")</f>
-        <v>2</v>
-      </c>
-      <c r="T28" s="35" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="64" t="s">
-        <v>281</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="C29" s="25">
-        <v>3</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32">
-        <f>COUNTA(D29:N29)-COUNTIF(D29:N29,"no honest gym equivalent")</f>
-        <v>0</v>
-      </c>
-      <c r="T29" s="35" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="64" t="s">
-        <v>288</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="C30" s="25">
-        <v>3</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="O30" s="32"/>
-      <c r="P30" s="32">
-        <f>COUNTA(D30:N30)-COUNTIF(D30:N30,"no honest gym equivalent")</f>
-        <v>0</v>
-      </c>
-      <c r="T30" s="35" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:22" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="28" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="34" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:V1"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="U5:U12 U14:U17 U19:U22 U24:U30" xr:uid="{DCE8C963-AD8A-FC4F-A79C-C395C8540AEB}">
-      <formula1>"keep,change,discuss"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>